--- a/test_notebooks_R/print_04_27_2022.xlsx
+++ b/test_notebooks_R/print_04_27_2022.xlsx
@@ -1595,34 +1595,40 @@
     <t xml:space="preserve">1x8 Oz. Pepitas</t>
   </si>
   <si>
+    <t xml:space="preserve">Smart, Annie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x14 Oz. Walnuts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Strembicki, Kate</t>
   </si>
   <si>
+    <t xml:space="preserve">Wagner, Elizabeth</t>
+  </si>
+  <si>
     <t xml:space="preserve">➕🐄[*]2x64 Oz. Milk - Whole</t>
   </si>
   <si>
-    <t xml:space="preserve">1x14 Oz. Walnuts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smart, Annie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wagner, Elizabeth</t>
+    <t xml:space="preserve">1x1 Each Fatayer - Cheese - Froz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x1 Pack Milk Chocolate Salted Bark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parker, Jean &amp; Hal</t>
   </si>
   <si>
     <t xml:space="preserve">White, Barbara</t>
   </si>
   <si>
-    <t xml:space="preserve">1x1 Each Fatayer - Cheese - Froz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x1 Pack Milk Chocolate Salted Bark</t>
-  </si>
-  <si>
     <t xml:space="preserve">1x1 Pack Pork Sausage - s&amp;p</t>
   </si>
   <si>
-    <t xml:space="preserve">Parker, Jean &amp; Hal</t>
+    <t xml:space="preserve">➕3x24 Oz. Yogurt - Plain Regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sechrist, Lois &amp; Bryan</t>
   </si>
   <si>
     <t xml:space="preserve">Rao, Roschan</t>
@@ -1637,69 +1643,63 @@
     <t xml:space="preserve">Smith, Jennifer &amp; Brendan</t>
   </si>
   <si>
-    <t xml:space="preserve">➕3x24 Oz. Yogurt - Plain Regular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sechrist, Lois &amp; Bryan</t>
+    <t xml:space="preserve">Stanley, Heather</t>
   </si>
   <si>
     <t xml:space="preserve">Westensee, Laura</t>
   </si>
   <si>
+    <t xml:space="preserve">➕2x1 Quart Jar Tomatoes</t>
+  </si>
+  <si>
     <t xml:space="preserve">1x1 Tub Chickpea Hummus</t>
   </si>
   <si>
-    <t xml:space="preserve">Stanley, Heather</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aubuchon, Myra and Jimmy</t>
   </si>
   <si>
-    <t xml:space="preserve">➕2x1 Quart Jar Tomatoes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coates, Andrea</t>
   </si>
   <si>
+    <t xml:space="preserve">🐄[*]1x64 Oz. Milk - Skim</t>
+  </si>
+  <si>
     <t xml:space="preserve">Getz, Ann</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]1x64 Oz. Milk - Skim</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hollingsworth, Meili</t>
   </si>
   <si>
     <t xml:space="preserve">Littleton, Rebecca</t>
   </si>
   <si>
+    <t xml:space="preserve">Love, Genevieve</t>
+  </si>
+  <si>
     <t xml:space="preserve">1xea. YoBul plain yogurt</t>
   </si>
   <si>
     <t xml:space="preserve">1x16 Ounce Cream pint</t>
   </si>
   <si>
-    <t xml:space="preserve">Love, Genevieve</t>
+    <t xml:space="preserve">1x1 Tub Gluten Free Black Beans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x1 Each Meatballs - Wee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Person, Jim</t>
   </si>
   <si>
     <t xml:space="preserve">Morley, Deborah</t>
   </si>
   <si>
-    <t xml:space="preserve">1x1 Tub Gluten Free Black Beans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x1 Each Meatballs - Wee</t>
-  </si>
-  <si>
     <t xml:space="preserve">1x1 Each FF Salad - Broccoli</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Pint FF Soup - Gumbo</t>
   </si>
   <si>
-    <t xml:space="preserve">Person, Jim</t>
-  </si>
-  <si>
     <t xml:space="preserve">Posega, Anne/Chris</t>
   </si>
   <si>
@@ -1709,34 +1709,34 @@
     <t xml:space="preserve">Batten, Guinn</t>
   </si>
   <si>
+    <t xml:space="preserve">1xDelivery Handling/Delivery fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">➕2x1 Each Granola Bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">➕3x1 Each Salmon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Moss, Elaine</t>
   </si>
   <si>
-    <t xml:space="preserve">1xDelivery Handling/Delivery fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">➕2x1 Each Granola Bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">➕3x1 Each Salmon</t>
+    <t xml:space="preserve">1x12 Oz. Stringbean Disco Inferno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulherin, Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proctor, Frank</t>
   </si>
   <si>
     <t xml:space="preserve">Pierce, Lois</t>
   </si>
   <si>
-    <t xml:space="preserve">1x12 Oz. Stringbean Disco Inferno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulherin, Ryan</t>
+    <t xml:space="preserve">➕2x1 Bottle Catsup - Marina's</t>
   </si>
   <si>
     <t xml:space="preserve">Stalnaker, David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proctor, Frank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">➕2x1 Bottle Catsup - Marina's</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Each Swiss Cheese - Ropp</t>
@@ -10143,7 +10143,7 @@
     </row>
     <row r="1142">
       <c r="A1142" t="s">
-        <v>528</v>
+        <v>24</v>
       </c>
       <c r="B1142" t="s">
         <v>58</v>
@@ -10151,7 +10151,7 @@
     </row>
     <row r="1143">
       <c r="A1143" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1143" t="s">
         <v>240</v>
@@ -10159,15 +10159,15 @@
     </row>
     <row r="1144">
       <c r="A1144" t="s">
-        <v>24</v>
+        <v>314</v>
       </c>
       <c r="B1144" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B1145" t="s">
         <v>7</v>
@@ -10175,41 +10175,25 @@
     </row>
     <row r="1146">
       <c r="A1146" t="s">
-        <v>350</v>
-      </c>
-      <c r="B1146" s="1" t="s">
-        <v>530</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B1146"/>
     </row>
     <row r="1147">
-      <c r="A1147" t="s">
-        <v>494</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>312</v>
-      </c>
+      <c r="A1147"/>
+      <c r="B1147"/>
     </row>
     <row r="1148">
-      <c r="A1148" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1148" s="3" t="s">
-        <v>396</v>
-      </c>
+      <c r="A1148"/>
+      <c r="B1148"/>
     </row>
     <row r="1149">
-      <c r="A1149" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>24</v>
-      </c>
+      <c r="A1149"/>
+      <c r="B1149"/>
     </row>
     <row r="1150">
       <c r="A1150"/>
-      <c r="B1150" t="s">
-        <v>10</v>
-      </c>
+      <c r="B1150"/>
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="s">
@@ -10221,10 +10205,10 @@
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B1152" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1153">
@@ -10245,304 +10229,310 @@
     </row>
     <row r="1155">
       <c r="A1155" t="s">
+        <v>531</v>
+      </c>
+      <c r="B1155" t="s">
         <v>75</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="s">
-        <v>533</v>
+        <v>15</v>
       </c>
       <c r="B1156" t="s">
-        <v>314</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="s">
-        <v>534</v>
+        <v>24</v>
       </c>
       <c r="B1157" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1158" t="s">
         <v>221</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="B1159" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1160">
-      <c r="A1160" s="1" t="s">
-        <v>536</v>
+      <c r="A1160" t="s">
+        <v>494</v>
       </c>
       <c r="B1160" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="s">
-        <v>312</v>
+        <v>27</v>
       </c>
       <c r="B1161" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="1162">
-      <c r="A1162" s="3" t="s">
-        <v>422</v>
+      <c r="A1162" t="s">
+        <v>7</v>
       </c>
       <c r="B1162" s="3" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="1163">
-      <c r="A1163" t="s">
+      <c r="A1163" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B1163" t="s">
         <v>6</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1164" t="s">
         <v>103</v>
       </c>
-      <c r="B1164" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="1165">
-      <c r="A1165" t="s">
+      <c r="A1165" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1165" t="s">
         <v>32</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1166" t="s">
         <v>57</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1167" t="s">
         <v>18</v>
-      </c>
-      <c r="B1167" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B1168" t="s">
-        <v>312</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1169" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1170" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1172" s="3" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="1170">
-      <c r="A1170" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="B1170" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="1171">
-      <c r="A1171" t="s">
-        <v>312</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" s="3" t="s">
+    <row r="1173">
+      <c r="A1173" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B1172" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="s">
+      <c r="B1173" t="s">
         <v>6</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1174" t="s">
         <v>181</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1175" t="s">
         <v>56</v>
-      </c>
-      <c r="B1175" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1176" t="s">
         <v>49</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1177" t="s">
         <v>57</v>
       </c>
-      <c r="B1177" s="3" t="s">
-        <v>422</v>
-      </c>
     </row>
     <row r="1178">
-      <c r="A1178" t="s">
+      <c r="A1178" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1178" t="s">
         <v>18</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1179" t="s">
         <v>240</v>
       </c>
-      <c r="B1179" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="1180">
-      <c r="A1180" t="s">
+      <c r="A1180" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1180" t="s">
         <v>145</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="s">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="B1181" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1182">
-      <c r="A1182" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>82</v>
+      <c r="A1182" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1182" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1183" t="s">
         <v>312</v>
       </c>
-      <c r="B1183" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="1184">
-      <c r="A1184" s="3" t="s">
+      <c r="A1184" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1184" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="B1184" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1185" t="s">
         <v>6</v>
       </c>
-      <c r="B1185" t="s">
-        <v>312</v>
-      </c>
     </row>
     <row r="1186">
-      <c r="A1186" t="s">
-        <v>547</v>
-      </c>
-      <c r="B1186" s="3" t="s">
-        <v>443</v>
+      <c r="A1186" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1187" t="s">
         <v>10</v>
       </c>
-      <c r="B1187" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="1188">
-      <c r="A1188" t="s">
-        <v>7</v>
+      <c r="A1188" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="B1188" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1189">
-      <c r="A1189"/>
-      <c r="B1189" t="s">
-        <v>6</v>
-      </c>
+      <c r="A1189" t="s">
+        <v>546</v>
+      </c>
+      <c r="B1189"/>
     </row>
     <row r="1190">
-      <c r="A1190"/>
-      <c r="B1190" t="s">
-        <v>12</v>
-      </c>
+      <c r="A1190" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1190"/>
     </row>
     <row r="1191">
-      <c r="A1191"/>
-      <c r="B1191" t="s">
-        <v>7</v>
-      </c>
+      <c r="A1191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1191"/>
     </row>
     <row r="1192">
-      <c r="A1192"/>
+      <c r="A1192" t="s">
+        <v>27</v>
+      </c>
       <c r="B1192"/>
     </row>
     <row r="1193">
-      <c r="A1193"/>
+      <c r="A1193" t="s">
+        <v>82</v>
+      </c>
       <c r="B1193"/>
     </row>
     <row r="1194">
-      <c r="A1194"/>
+      <c r="A1194" t="s">
+        <v>7</v>
+      </c>
       <c r="B1194"/>
     </row>
     <row r="1195">
@@ -10563,10 +10553,10 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1198" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B1198" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="1199">
@@ -10587,71 +10577,71 @@
     </row>
     <row r="1201">
       <c r="A1201" t="s">
-        <v>550</v>
+        <v>172</v>
       </c>
       <c r="B1201" t="s">
-        <v>63</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1202" t="s">
         <v>181</v>
-      </c>
-      <c r="B1202" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1203" t="s">
         <v>78</v>
-      </c>
-      <c r="B1203" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1204" t="s">
         <v>526</v>
-      </c>
-      <c r="B1204" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1205" t="s">
         <v>203</v>
       </c>
-      <c r="B1205" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="1206">
-      <c r="A1206" t="s">
-        <v>7</v>
+      <c r="A1206" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="B1206" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1207">
-      <c r="A1207" s="1" t="s">
+      <c r="A1207" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1207" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B1207" s="1" t="s">
-        <v>552</v>
-      </c>
     </row>
     <row r="1208">
-      <c r="A1208" t="s">
-        <v>312</v>
+      <c r="A1208" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="B1208" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="1209">
-      <c r="A1209" s="3" t="s">
-        <v>443</v>
+      <c r="A1209" t="s">
+        <v>63</v>
       </c>
       <c r="B1209" s="3" t="s">
         <v>443</v>
@@ -10659,106 +10649,106 @@
     </row>
     <row r="1210">
       <c r="A1210" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1210" t="s">
         <v>15</v>
-      </c>
-      <c r="B1210" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1211" t="s">
         <v>148</v>
-      </c>
-      <c r="B1211" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1212" t="s">
         <v>24</v>
-      </c>
-      <c r="B1212" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1213" t="s">
         <v>211</v>
-      </c>
-      <c r="B1213" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1214" t="s">
         <v>76</v>
       </c>
-      <c r="B1214" t="s">
-        <v>503</v>
-      </c>
     </row>
     <row r="1215">
-      <c r="A1215" t="s">
-        <v>7</v>
+      <c r="A1215" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="B1215" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1216">
-      <c r="A1216" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="B1216" t="s">
-        <v>494</v>
+      <c r="A1216" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1216" s="1" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="1217">
-      <c r="A1217" t="s">
+      <c r="A1217" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1217" t="s">
         <v>312</v>
       </c>
-      <c r="B1217" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="1218">
-      <c r="A1218" s="3" t="s">
+      <c r="A1218" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1218" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="B1218" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1219" t="s">
         <v>6</v>
-      </c>
-      <c r="B1219" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B1220" t="s">
-        <v>312</v>
+        <v>556</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="s">
-        <v>558</v>
-      </c>
-      <c r="B1221" s="3" t="s">
-        <v>443</v>
+        <v>314</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1222" t="s">
         <v>11</v>
-      </c>
-      <c r="B1222" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="1223">
@@ -10766,139 +10756,137 @@
         <v>57</v>
       </c>
       <c r="B1223" t="s">
-        <v>559</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="s">
-        <v>7</v>
+        <v>494</v>
       </c>
       <c r="B1224" t="s">
-        <v>560</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1225">
-      <c r="A1225" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="B1225" t="s">
-        <v>246</v>
+      <c r="A1225" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1225" s="1" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1226" t="s">
         <v>312</v>
       </c>
-      <c r="B1226" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="1227">
-      <c r="A1227" s="3" t="s">
+      <c r="A1227" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1227" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="B1227" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1228" t="s">
         <v>6</v>
       </c>
-      <c r="B1228" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="1229">
-      <c r="A1229" t="s">
+      <c r="A1229" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B1229" t="s">
         <v>24</v>
-      </c>
-      <c r="B1229" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1230" t="s">
         <v>515</v>
-      </c>
-      <c r="B1230" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1231" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s">
+        <v>561</v>
+      </c>
+      <c r="B1232" s="1" t="s">
         <v>562</v>
-      </c>
-    </row>
-    <row r="1232">
-      <c r="A1232" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="B1232" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1233" t="s">
         <v>312</v>
       </c>
-      <c r="B1233" s="3" t="s">
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1234" s="3" t="s">
         <v>443</v>
-      </c>
-    </row>
-    <row r="1234">
-      <c r="A1234" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="B1235" t="s">
-        <v>209</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B1236" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B1237" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="s">
-        <v>398</v>
+        <v>7</v>
       </c>
       <c r="B1238" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1239">
-      <c r="A1239" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1239"/>
+      <c r="A1239"/>
+      <c r="B1239" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1240">
-      <c r="A1240" t="s">
-        <v>7</v>
-      </c>
+      <c r="A1240"/>
       <c r="B1240"/>
     </row>
     <row r="1241">
@@ -10919,10 +10907,10 @@
     </row>
     <row r="1244">
       <c r="A1244" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B1244" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="B1244" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="1245">
@@ -10934,191 +10922,209 @@
       </c>
     </row>
     <row r="1246">
-      <c r="A1246" t="s">
-        <v>566</v>
+      <c r="A1246" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="B1246" t="s">
-        <v>6</v>
+        <v>565</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1247" t="s">
         <v>63</v>
-      </c>
-      <c r="B1247" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1248" t="s">
         <v>156</v>
-      </c>
-      <c r="B1248" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="s">
-        <v>567</v>
+        <v>25</v>
       </c>
       <c r="B1249" t="s">
-        <v>11</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="s">
-        <v>568</v>
+        <v>398</v>
       </c>
       <c r="B1250" t="s">
-        <v>57</v>
+        <v>567</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1251" t="s">
         <v>76</v>
-      </c>
-      <c r="B1251" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1252" t="s">
         <v>18</v>
       </c>
-      <c r="B1252" s="1" t="s">
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B1253" t="s">
         <v>569</v>
-      </c>
-    </row>
-    <row r="1253">
-      <c r="A1253" t="s">
-        <v>570</v>
-      </c>
-      <c r="B1253" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1254" s="2" t="s">
-        <v>5</v>
+        <v>312</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1255">
-      <c r="A1255" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="B1255" t="s">
-        <v>7</v>
+      <c r="A1255" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1255" s="1" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1256" t="s">
         <v>312</v>
       </c>
-      <c r="B1256" s="1" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="1257">
-      <c r="A1257" s="2" t="s">
+      <c r="A1257" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1257" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B1257" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B1258" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1259">
-      <c r="A1259" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="B1259" t="s">
-        <v>10</v>
+      <c r="A1259" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1259" s="1" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1260" t="s">
         <v>312</v>
       </c>
-      <c r="B1260" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="1261">
-      <c r="A1261" t="s">
-        <v>574</v>
+      <c r="A1261" s="1" t="s">
+        <v>572</v>
       </c>
       <c r="B1261" t="s">
-        <v>11</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1262" t="s">
         <v>275</v>
       </c>
-      <c r="B1262" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="1263">
-      <c r="A1263" t="s">
+      <c r="A1263" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1263" t="s">
         <v>24</v>
       </c>
-      <c r="B1263"/>
     </row>
     <row r="1264">
       <c r="A1264" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1264" t="s">
         <v>10</v>
       </c>
-      <c r="B1264"/>
     </row>
     <row r="1265">
-      <c r="A1265" t="s">
+      <c r="A1265" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B1265" t="s">
         <v>314</v>
       </c>
-      <c r="B1265"/>
     </row>
     <row r="1266">
       <c r="A1266" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1266" t="s">
         <v>388</v>
       </c>
-      <c r="B1266"/>
     </row>
     <row r="1267">
       <c r="A1267" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1267" t="s">
         <v>57</v>
       </c>
-      <c r="B1267"/>
     </row>
     <row r="1268">
       <c r="A1268" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1268" t="s">
         <v>27</v>
       </c>
-      <c r="B1268"/>
     </row>
     <row r="1269">
       <c r="A1269" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1269" t="s">
         <v>575</v>
       </c>
-      <c r="B1269"/>
     </row>
     <row r="1270">
       <c r="A1270" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1270"/>
+        <v>11</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1271">
-      <c r="A1271"/>
+      <c r="A1271" t="s">
+        <v>7</v>
+      </c>
       <c r="B1271"/>
     </row>
     <row r="1272">
@@ -11191,2403 +11197,2413 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1">
+    <cfRule type="expression" dxfId="0" priority="482">
+      <formula>A1&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A2">
+    <cfRule type="expression" dxfId="0" priority="481">
+      <formula>A2&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:A7">
     <cfRule type="expression" dxfId="0" priority="480">
-      <formula>A1&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A2">
+      <formula>A7&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:A22">
     <cfRule type="expression" dxfId="0" priority="479">
-      <formula>A2&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A7">
+      <formula>A22&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A31">
     <cfRule type="expression" dxfId="0" priority="478">
-      <formula>A7&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A22">
+      <formula>A31&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47:A47">
     <cfRule type="expression" dxfId="0" priority="477">
-      <formula>A22&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A31">
+      <formula>A47&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:A48">
     <cfRule type="expression" dxfId="0" priority="476">
-      <formula>A31&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:A47">
+      <formula>A48&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60:A60">
     <cfRule type="expression" dxfId="0" priority="475">
-      <formula>A47&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48:A48">
+      <formula>A60&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72:A72">
     <cfRule type="expression" dxfId="0" priority="474">
-      <formula>A48&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60:A60">
+      <formula>A72&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A84:A84">
     <cfRule type="expression" dxfId="0" priority="473">
-      <formula>A60&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A72:A72">
+      <formula>A84&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A93:A93">
     <cfRule type="expression" dxfId="0" priority="472">
-      <formula>A72&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A84:A84">
+      <formula>A93&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A94:A94">
     <cfRule type="expression" dxfId="0" priority="471">
-      <formula>A84&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A93:A93">
+      <formula>A94&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104:A104">
     <cfRule type="expression" dxfId="0" priority="470">
-      <formula>A93&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A94:A94">
+      <formula>A104&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A111:A111">
     <cfRule type="expression" dxfId="0" priority="469">
-      <formula>A94&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A104:A104">
+      <formula>A111&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A121:A121">
     <cfRule type="expression" dxfId="0" priority="468">
-      <formula>A104&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A111:A111">
+      <formula>A121&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A128:A128">
     <cfRule type="expression" dxfId="0" priority="467">
-      <formula>A111&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A121:A121">
+      <formula>A128&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A139:A139">
     <cfRule type="expression" dxfId="0" priority="466">
-      <formula>A121&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A128:A128">
+      <formula>A139&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A140:A140">
     <cfRule type="expression" dxfId="0" priority="465">
-      <formula>A128&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A139:A139">
+      <formula>A140&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A145:A145">
     <cfRule type="expression" dxfId="0" priority="464">
-      <formula>A139&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A140:A140">
+      <formula>A145&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A155:A155">
     <cfRule type="expression" dxfId="0" priority="463">
-      <formula>A140&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A145:A145">
-    <cfRule type="expression" dxfId="0" priority="462">
-      <formula>A145&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A155:A155">
-    <cfRule type="expression" dxfId="0" priority="461">
       <formula>A155&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A185:A185">
+    <cfRule type="expression" dxfId="1" priority="462">
+      <formula>A185&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A186:A186">
+    <cfRule type="expression" dxfId="1" priority="461">
+      <formula>A186&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A195:A195">
     <cfRule type="expression" dxfId="1" priority="460">
-      <formula>A185&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A186:A186">
+      <formula>A195&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A204:A204">
     <cfRule type="expression" dxfId="1" priority="459">
-      <formula>A186&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A195:A195">
+      <formula>A204&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A212:A212">
     <cfRule type="expression" dxfId="1" priority="458">
-      <formula>A195&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A204:A204">
+      <formula>A212&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A231:A231">
     <cfRule type="expression" dxfId="1" priority="457">
-      <formula>A204&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A212:A212">
+      <formula>A231&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A232:A232">
     <cfRule type="expression" dxfId="1" priority="456">
-      <formula>A212&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A231:A231">
+      <formula>A232&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A243:A243">
     <cfRule type="expression" dxfId="1" priority="455">
-      <formula>A231&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A232:A232">
+      <formula>A243&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A253:A253">
     <cfRule type="expression" dxfId="1" priority="454">
-      <formula>A232&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A243:A243">
+      <formula>A253&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A263:A263">
     <cfRule type="expression" dxfId="1" priority="453">
-      <formula>A243&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A253:A253">
+      <formula>A263&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A277:A277">
     <cfRule type="expression" dxfId="1" priority="452">
-      <formula>A253&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A263:A263">
+      <formula>A277&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A278:A278">
     <cfRule type="expression" dxfId="1" priority="451">
-      <formula>A263&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A277:A277">
+      <formula>A278&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A292:A292">
     <cfRule type="expression" dxfId="1" priority="450">
-      <formula>A277&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A278:A278">
+      <formula>A292&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A301:A301">
     <cfRule type="expression" dxfId="1" priority="449">
-      <formula>A278&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A292:A292">
+      <formula>A301&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A305:A305">
     <cfRule type="expression" dxfId="1" priority="448">
-      <formula>A292&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A301:A301">
-    <cfRule type="expression" dxfId="1" priority="447">
-      <formula>A301&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A305:A305">
-    <cfRule type="expression" dxfId="1" priority="446">
       <formula>A305&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A323:A323">
+    <cfRule type="expression" dxfId="2" priority="447">
+      <formula>A323&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A324:A324">
+    <cfRule type="expression" dxfId="2" priority="446">
+      <formula>A324&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A335:A335">
     <cfRule type="expression" dxfId="2" priority="445">
-      <formula>A323&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A324:A324">
+      <formula>A335&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A346:A346">
     <cfRule type="expression" dxfId="2" priority="444">
-      <formula>A324&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A335:A335">
+      <formula>A346&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A369">
     <cfRule type="expression" dxfId="2" priority="443">
-      <formula>A335&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A346:A346">
+      <formula>A369&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A370:A370">
     <cfRule type="expression" dxfId="2" priority="442">
-      <formula>A346&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A369:A369">
+      <formula>A370&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A381:A381">
     <cfRule type="expression" dxfId="2" priority="441">
-      <formula>A369&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A370:A370">
+      <formula>A381&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A390:A390">
     <cfRule type="expression" dxfId="2" priority="440">
-      <formula>A370&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A381:A381">
+      <formula>A390&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A400:A400">
     <cfRule type="expression" dxfId="2" priority="439">
-      <formula>A381&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A390:A390">
+      <formula>A400&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A415:A415">
     <cfRule type="expression" dxfId="2" priority="438">
-      <formula>A390&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A400:A400">
+      <formula>A415&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A416:A416">
     <cfRule type="expression" dxfId="2" priority="437">
-      <formula>A400&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A415:A415">
+      <formula>A416&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A427:A427">
     <cfRule type="expression" dxfId="2" priority="436">
-      <formula>A415&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A416:A416">
+      <formula>A427&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A431:A431">
     <cfRule type="expression" dxfId="2" priority="435">
-      <formula>A416&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A427:A427">
-    <cfRule type="expression" dxfId="2" priority="434">
-      <formula>A427&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A431:A431">
-    <cfRule type="expression" dxfId="2" priority="433">
       <formula>A431&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A461:A461">
+    <cfRule type="expression" dxfId="3" priority="434">
+      <formula>A461&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A462:A462">
+    <cfRule type="expression" dxfId="3" priority="433">
+      <formula>A462&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A475:A475">
     <cfRule type="expression" dxfId="3" priority="432">
-      <formula>A461&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A462:A462">
+      <formula>A475&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A491:A491">
     <cfRule type="expression" dxfId="3" priority="431">
-      <formula>A462&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A475:A475">
+      <formula>A491&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A507:A507">
     <cfRule type="expression" dxfId="3" priority="430">
-      <formula>A475&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A491:A491">
+      <formula>A507&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A508:A508">
     <cfRule type="expression" dxfId="3" priority="429">
-      <formula>A491&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A507:A507">
-    <cfRule type="expression" dxfId="3" priority="428">
-      <formula>A507&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A508:A508">
-    <cfRule type="expression" dxfId="3" priority="427">
       <formula>A508&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A553:A553">
+    <cfRule type="expression" dxfId="4" priority="428">
+      <formula>A553&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A554:A554">
+    <cfRule type="expression" dxfId="4" priority="427">
+      <formula>A554&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A564:A564">
     <cfRule type="expression" dxfId="4" priority="426">
-      <formula>A553&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A554:A554">
+      <formula>A564&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A575:A575">
     <cfRule type="expression" dxfId="4" priority="425">
-      <formula>A554&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A564:A564">
+      <formula>A575&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A585:A585">
     <cfRule type="expression" dxfId="4" priority="424">
-      <formula>A564&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A575:A575">
+      <formula>A585&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A599:A599">
     <cfRule type="expression" dxfId="4" priority="423">
-      <formula>A575&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A585:A585">
+      <formula>A599&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A600:A600">
     <cfRule type="expression" dxfId="4" priority="422">
-      <formula>A585&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A599:A599">
+      <formula>A600&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A617:A617">
     <cfRule type="expression" dxfId="4" priority="421">
-      <formula>A599&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A600:A600">
+      <formula>A617&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A624:A624">
     <cfRule type="expression" dxfId="4" priority="420">
-      <formula>A600&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A617:A617">
+      <formula>A624&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A632:A632">
     <cfRule type="expression" dxfId="4" priority="419">
-      <formula>A617&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A624:A624">
+      <formula>A632&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A645:A645">
     <cfRule type="expression" dxfId="4" priority="418">
-      <formula>A624&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A632:A632">
+      <formula>A645&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A646:A646">
     <cfRule type="expression" dxfId="4" priority="417">
-      <formula>A632&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A645:A645">
+      <formula>A646&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A656:A656">
     <cfRule type="expression" dxfId="4" priority="416">
-      <formula>A645&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A646:A646">
+      <formula>A656&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A663:A663">
     <cfRule type="expression" dxfId="4" priority="415">
-      <formula>A646&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A656:A656">
+      <formula>A663&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A672:A672">
     <cfRule type="expression" dxfId="4" priority="414">
-      <formula>A656&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A663:A663">
+      <formula>A672&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A691:A691">
     <cfRule type="expression" dxfId="4" priority="413">
-      <formula>A663&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A672:A672">
+      <formula>A691&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A692:A692">
     <cfRule type="expression" dxfId="4" priority="412">
-      <formula>A672&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A691:A691">
+      <formula>A692&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A702:A702">
     <cfRule type="expression" dxfId="4" priority="411">
-      <formula>A691&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A692:A692">
+      <formula>A702&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A710:A710">
     <cfRule type="expression" dxfId="4" priority="410">
-      <formula>A692&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A702:A702">
+      <formula>A710&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A718:A718">
     <cfRule type="expression" dxfId="4" priority="409">
-      <formula>A702&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A710:A710">
+      <formula>A718&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A725:A725">
     <cfRule type="expression" dxfId="4" priority="408">
-      <formula>A710&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A718:A718">
+      <formula>A725&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A737:A737">
     <cfRule type="expression" dxfId="4" priority="407">
-      <formula>A718&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A725:A725">
+      <formula>A737&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A738:A738">
     <cfRule type="expression" dxfId="4" priority="406">
-      <formula>A725&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A737:A737">
+      <formula>A738&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A752:A752">
     <cfRule type="expression" dxfId="4" priority="405">
-      <formula>A737&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A738:A738">
-    <cfRule type="expression" dxfId="4" priority="404">
-      <formula>A738&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A752:A752">
-    <cfRule type="expression" dxfId="4" priority="403">
       <formula>A752&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A783:A783">
+    <cfRule type="expression" dxfId="5" priority="404">
+      <formula>A783&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A784:A784">
+    <cfRule type="expression" dxfId="5" priority="403">
+      <formula>A784&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A801:A801">
     <cfRule type="expression" dxfId="5" priority="402">
-      <formula>A783&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A784:A784">
+      <formula>A801&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A810:A810">
     <cfRule type="expression" dxfId="5" priority="401">
-      <formula>A784&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A801:A801">
+      <formula>A810&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A818:A818">
     <cfRule type="expression" dxfId="5" priority="400">
-      <formula>A801&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A810:A810">
+      <formula>A818&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A829:A829">
     <cfRule type="expression" dxfId="5" priority="399">
-      <formula>A810&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A818:A818">
+      <formula>A829&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A830:A830">
     <cfRule type="expression" dxfId="5" priority="398">
-      <formula>A818&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A829:A829">
+      <formula>A830&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A838:A838">
     <cfRule type="expression" dxfId="5" priority="397">
-      <formula>A829&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A830:A830">
+      <formula>A838&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A846:A846">
     <cfRule type="expression" dxfId="5" priority="396">
-      <formula>A830&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A838:A838">
+      <formula>A846&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A854:A854">
     <cfRule type="expression" dxfId="5" priority="395">
-      <formula>A838&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A846:A846">
+      <formula>A854&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A875:A875">
     <cfRule type="expression" dxfId="5" priority="394">
-      <formula>A846&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A854:A854">
+      <formula>A875&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A876:A876">
     <cfRule type="expression" dxfId="5" priority="393">
-      <formula>A854&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A875:A875">
+      <formula>A876&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A887:A887">
     <cfRule type="expression" dxfId="5" priority="392">
-      <formula>A875&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A876:A876">
+      <formula>A887&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A898:A898">
     <cfRule type="expression" dxfId="5" priority="391">
-      <formula>A876&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A887:A887">
+      <formula>A898&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A902:A902">
     <cfRule type="expression" dxfId="5" priority="390">
-      <formula>A887&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A898:A898">
+      <formula>A902&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A913:A913">
     <cfRule type="expression" dxfId="5" priority="389">
-      <formula>A898&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A902:A902">
+      <formula>A913&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A921:A921">
     <cfRule type="expression" dxfId="5" priority="388">
-      <formula>A902&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A913:A913">
+      <formula>A921&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A922:A922">
     <cfRule type="expression" dxfId="5" priority="387">
-      <formula>A913&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A921:A921">
+      <formula>A922&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A933:A933">
     <cfRule type="expression" dxfId="5" priority="386">
-      <formula>A921&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A922:A922">
-    <cfRule type="expression" dxfId="5" priority="385">
-      <formula>A922&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A933:A933">
-    <cfRule type="expression" dxfId="5" priority="384">
       <formula>A933&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A967:A967">
+    <cfRule type="expression" dxfId="6" priority="385">
+      <formula>A967&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A968:A968">
+    <cfRule type="expression" dxfId="6" priority="384">
+      <formula>A968&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A976:A976">
     <cfRule type="expression" dxfId="6" priority="383">
-      <formula>A967&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A968:A968">
+      <formula>A976&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A983:A983">
     <cfRule type="expression" dxfId="6" priority="382">
-      <formula>A968&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A976:A976">
+      <formula>A983&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A994:A994">
     <cfRule type="expression" dxfId="6" priority="381">
-      <formula>A976&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A983:A983">
+      <formula>A994&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1013:A1013">
     <cfRule type="expression" dxfId="6" priority="380">
-      <formula>A983&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A994:A994">
+      <formula>A1013&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1014:A1014">
     <cfRule type="expression" dxfId="6" priority="379">
-      <formula>A994&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1013:A1013">
+      <formula>A1014&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1026:A1026">
     <cfRule type="expression" dxfId="6" priority="378">
-      <formula>A1013&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1014:A1014">
+      <formula>A1026&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1039:A1039">
     <cfRule type="expression" dxfId="6" priority="377">
-      <formula>A1014&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1026:A1026">
+      <formula>A1039&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1043:A1043">
     <cfRule type="expression" dxfId="6" priority="376">
-      <formula>A1026&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1039:A1039">
+      <formula>A1043&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1047:A1047">
     <cfRule type="expression" dxfId="6" priority="375">
-      <formula>A1039&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1043:A1043">
-    <cfRule type="expression" dxfId="6" priority="374">
-      <formula>A1043&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1047:A1047">
-    <cfRule type="expression" dxfId="6" priority="373">
       <formula>A1047&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1059:A1059">
-    <cfRule type="expression" dxfId="7" priority="372">
+    <cfRule type="expression" dxfId="7" priority="374">
       <formula>A1059&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1060:A1060">
-    <cfRule type="expression" dxfId="7" priority="371">
+    <cfRule type="expression" dxfId="7" priority="373">
       <formula>A1060&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1105:A1105">
+    <cfRule type="expression" dxfId="8" priority="372">
+      <formula>A1105&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1106:A1106">
+    <cfRule type="expression" dxfId="8" priority="371">
+      <formula>A1106&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1112:A1112">
     <cfRule type="expression" dxfId="8" priority="370">
-      <formula>A1105&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1106:A1106">
+      <formula>A1112&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1122:A1122">
     <cfRule type="expression" dxfId="8" priority="369">
-      <formula>A1106&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1112:A1112">
+      <formula>A1122&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1131:A1131">
     <cfRule type="expression" dxfId="8" priority="368">
-      <formula>A1112&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1122:A1122">
+      <formula>A1131&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1139:A1139">
     <cfRule type="expression" dxfId="8" priority="367">
-      <formula>A1122&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1131:A1131">
+      <formula>A1139&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1151:A1151">
     <cfRule type="expression" dxfId="8" priority="366">
-      <formula>A1131&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1139:A1139">
+      <formula>A1151&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1152:A1152">
     <cfRule type="expression" dxfId="8" priority="365">
-      <formula>A1139&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1151:A1151">
+      <formula>A1152&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1163:A1163">
     <cfRule type="expression" dxfId="8" priority="364">
-      <formula>A1151&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1152:A1152">
+      <formula>A1163&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1171:A1171">
     <cfRule type="expression" dxfId="8" priority="363">
-      <formula>A1152&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1160:A1160">
+      <formula>A1171&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1178:A1178">
     <cfRule type="expression" dxfId="8" priority="362">
-      <formula>A1160&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1170:A1170">
+      <formula>A1178&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1186:A1186">
     <cfRule type="expression" dxfId="8" priority="361">
-      <formula>A1170&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1182:A1182">
+      <formula>A1186&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1197:A1197">
     <cfRule type="expression" dxfId="8" priority="360">
-      <formula>A1182&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1197:A1197">
+      <formula>A1197&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1198:A1198">
     <cfRule type="expression" dxfId="8" priority="359">
-      <formula>A1197&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1198:A1198">
+      <formula>A1198&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1206:A1206">
     <cfRule type="expression" dxfId="8" priority="358">
-      <formula>A1198&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1207:A1207">
+      <formula>A1206&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1215:A1215">
     <cfRule type="expression" dxfId="8" priority="357">
-      <formula>A1207&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1216:A1216">
+      <formula>A1215&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1227:A1227">
     <cfRule type="expression" dxfId="8" priority="356">
-      <formula>A1216&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1225:A1225">
+      <formula>A1227&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1243:A1243">
     <cfRule type="expression" dxfId="8" priority="355">
-      <formula>A1225&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1232:A1232">
+      <formula>A1243&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1244:A1244">
     <cfRule type="expression" dxfId="8" priority="354">
-      <formula>A1232&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1243:A1243">
+      <formula>A1244&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1253:A1253">
     <cfRule type="expression" dxfId="8" priority="353">
-      <formula>A1243&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1244:A1244">
+      <formula>A1253&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1261:A1261">
     <cfRule type="expression" dxfId="8" priority="352">
-      <formula>A1244&lt;&gt;0</formula>
+      <formula>A1261&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1265:A1265">
+    <cfRule type="expression" dxfId="8" priority="351">
+      <formula>A1265&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1">
+    <cfRule type="expression" dxfId="0" priority="350">
+      <formula>B1&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B2">
+    <cfRule type="expression" dxfId="0" priority="349">
+      <formula>B2&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:B14">
+    <cfRule type="expression" dxfId="0" priority="348">
+      <formula>B14&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B25">
+    <cfRule type="expression" dxfId="0" priority="347">
+      <formula>B25&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B35">
+    <cfRule type="expression" dxfId="0" priority="346">
+      <formula>B35&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B47">
+    <cfRule type="expression" dxfId="0" priority="345">
+      <formula>B47&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B48">
+    <cfRule type="expression" dxfId="0" priority="344">
+      <formula>B48&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B59">
+    <cfRule type="expression" dxfId="0" priority="343">
+      <formula>B59&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68:B68">
+    <cfRule type="expression" dxfId="0" priority="342">
+      <formula>B68&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79:B79">
+    <cfRule type="expression" dxfId="0" priority="341">
+      <formula>B79&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93:B93">
+    <cfRule type="expression" dxfId="0" priority="340">
+      <formula>B93&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B94:B94">
+    <cfRule type="expression" dxfId="0" priority="339">
+      <formula>B94&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B103:B103">
+    <cfRule type="expression" dxfId="0" priority="338">
+      <formula>B103&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B113:B113">
+    <cfRule type="expression" dxfId="0" priority="337">
+      <formula>B113&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B124:B124">
+    <cfRule type="expression" dxfId="0" priority="336">
+      <formula>B124&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139:B139">
+    <cfRule type="expression" dxfId="0" priority="335">
+      <formula>B139&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140:B140">
+    <cfRule type="expression" dxfId="0" priority="334">
+      <formula>B140&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B148:B148">
+    <cfRule type="expression" dxfId="0" priority="333">
+      <formula>B148&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B185:B185">
+    <cfRule type="expression" dxfId="1" priority="332">
+      <formula>B185&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B186:B186">
+    <cfRule type="expression" dxfId="1" priority="331">
+      <formula>B186&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B194:B194">
+    <cfRule type="expression" dxfId="1" priority="330">
+      <formula>B194&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B208:B208">
+    <cfRule type="expression" dxfId="1" priority="329">
+      <formula>B208&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B217:B217">
+    <cfRule type="expression" dxfId="1" priority="328">
+      <formula>B217&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B231:B231">
+    <cfRule type="expression" dxfId="1" priority="327">
+      <formula>B231&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B232:B232">
+    <cfRule type="expression" dxfId="1" priority="326">
+      <formula>B232&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B240:B240">
+    <cfRule type="expression" dxfId="1" priority="325">
+      <formula>B240&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B253:B253">
+    <cfRule type="expression" dxfId="1" priority="324">
+      <formula>B253&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B277:B277">
+    <cfRule type="expression" dxfId="1" priority="323">
+      <formula>B277&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B278:B278">
+    <cfRule type="expression" dxfId="1" priority="322">
+      <formula>B278&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B283:B283">
+    <cfRule type="expression" dxfId="1" priority="321">
+      <formula>B283&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B291:B291">
+    <cfRule type="expression" dxfId="1" priority="320">
+      <formula>B291&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B295:B295">
+    <cfRule type="expression" dxfId="1" priority="319">
+      <formula>B295&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B323:B323">
+    <cfRule type="expression" dxfId="2" priority="318">
+      <formula>B323&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B324:B324">
+    <cfRule type="expression" dxfId="2" priority="317">
+      <formula>B324&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334:B334">
+    <cfRule type="expression" dxfId="2" priority="316">
+      <formula>B334&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B345:B345">
+    <cfRule type="expression" dxfId="2" priority="315">
+      <formula>B345&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B353:B353">
+    <cfRule type="expression" dxfId="2" priority="314">
+      <formula>B353&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B369:B369">
+    <cfRule type="expression" dxfId="2" priority="313">
+      <formula>B369&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B370:B370">
+    <cfRule type="expression" dxfId="2" priority="312">
+      <formula>B370&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B380:B380">
+    <cfRule type="expression" dxfId="2" priority="311">
+      <formula>B380&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B390:B390">
+    <cfRule type="expression" dxfId="2" priority="310">
+      <formula>B390&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B415:B415">
+    <cfRule type="expression" dxfId="2" priority="309">
+      <formula>B415&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B416:B416">
+    <cfRule type="expression" dxfId="2" priority="308">
+      <formula>B416&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B424:B424">
+    <cfRule type="expression" dxfId="2" priority="307">
+      <formula>B424&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B461:B461">
+    <cfRule type="expression" dxfId="3" priority="306">
+      <formula>B461&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B462:B462">
+    <cfRule type="expression" dxfId="3" priority="305">
+      <formula>B462&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B475:B475">
+    <cfRule type="expression" dxfId="3" priority="304">
+      <formula>B475&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B482:B482">
+    <cfRule type="expression" dxfId="3" priority="303">
+      <formula>B482&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B507:B507">
+    <cfRule type="expression" dxfId="3" priority="302">
+      <formula>B507&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B508:B508">
+    <cfRule type="expression" dxfId="3" priority="301">
+      <formula>B508&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B553:B553">
+    <cfRule type="expression" dxfId="4" priority="300">
+      <formula>B553&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B554:B554">
+    <cfRule type="expression" dxfId="4" priority="299">
+      <formula>B554&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B562:B562">
+    <cfRule type="expression" dxfId="4" priority="298">
+      <formula>B562&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B567:B567">
+    <cfRule type="expression" dxfId="4" priority="297">
+      <formula>B567&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B576:B576">
+    <cfRule type="expression" dxfId="4" priority="296">
+      <formula>B576&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B584:B584">
+    <cfRule type="expression" dxfId="4" priority="295">
+      <formula>B584&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B599:B599">
+    <cfRule type="expression" dxfId="4" priority="294">
+      <formula>B599&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B600:B600">
+    <cfRule type="expression" dxfId="4" priority="293">
+      <formula>B600&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B609:B609">
+    <cfRule type="expression" dxfId="4" priority="292">
+      <formula>B609&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B617:B617">
+    <cfRule type="expression" dxfId="4" priority="291">
+      <formula>B617&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B630:B630">
+    <cfRule type="expression" dxfId="4" priority="290">
+      <formula>B630&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B645:B645">
+    <cfRule type="expression" dxfId="4" priority="289">
+      <formula>B645&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B646:B646">
+    <cfRule type="expression" dxfId="4" priority="288">
+      <formula>B646&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B654:B654">
+    <cfRule type="expression" dxfId="4" priority="287">
+      <formula>B654&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B662:B662">
+    <cfRule type="expression" dxfId="4" priority="286">
+      <formula>B662&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B672:B672">
+    <cfRule type="expression" dxfId="4" priority="285">
+      <formula>B672&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B691:B691">
+    <cfRule type="expression" dxfId="4" priority="284">
+      <formula>B691&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B692:B692">
+    <cfRule type="expression" dxfId="4" priority="283">
+      <formula>B692&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B697:B697">
+    <cfRule type="expression" dxfId="4" priority="282">
+      <formula>B697&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B707:B707">
+    <cfRule type="expression" dxfId="4" priority="281">
+      <formula>B707&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B715:B715">
+    <cfRule type="expression" dxfId="4" priority="280">
+      <formula>B715&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B723:B723">
+    <cfRule type="expression" dxfId="4" priority="279">
+      <formula>B723&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B727:B727">
+    <cfRule type="expression" dxfId="4" priority="278">
+      <formula>B727&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B737:B737">
+    <cfRule type="expression" dxfId="4" priority="277">
+      <formula>B737&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B738:B738">
+    <cfRule type="expression" dxfId="4" priority="276">
+      <formula>B738&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B783:B783">
+    <cfRule type="expression" dxfId="5" priority="275">
+      <formula>B783&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B784:B784">
+    <cfRule type="expression" dxfId="5" priority="274">
+      <formula>B784&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B792:B792">
+    <cfRule type="expression" dxfId="5" priority="273">
+      <formula>B792&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B801:B801">
+    <cfRule type="expression" dxfId="5" priority="272">
+      <formula>B801&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B810:B810">
+    <cfRule type="expression" dxfId="5" priority="271">
+      <formula>B810&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B829:B829">
+    <cfRule type="expression" dxfId="5" priority="270">
+      <formula>B829&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B830:B830">
+    <cfRule type="expression" dxfId="5" priority="269">
+      <formula>B830&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B841:B841">
+    <cfRule type="expression" dxfId="5" priority="268">
+      <formula>B841&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B849:B849">
+    <cfRule type="expression" dxfId="5" priority="267">
+      <formula>B849&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B858:B858">
+    <cfRule type="expression" dxfId="5" priority="266">
+      <formula>B858&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B875:B875">
+    <cfRule type="expression" dxfId="5" priority="265">
+      <formula>B875&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B876:B876">
+    <cfRule type="expression" dxfId="5" priority="264">
+      <formula>B876&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B884:B884">
+    <cfRule type="expression" dxfId="5" priority="263">
+      <formula>B884&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893:B893">
+    <cfRule type="expression" dxfId="5" priority="262">
+      <formula>B893&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B904:B904">
+    <cfRule type="expression" dxfId="5" priority="261">
+      <formula>B904&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B921:B921">
+    <cfRule type="expression" dxfId="5" priority="260">
+      <formula>B921&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B922:B922">
+    <cfRule type="expression" dxfId="5" priority="259">
+      <formula>B922&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B932:B932">
+    <cfRule type="expression" dxfId="5" priority="258">
+      <formula>B932&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B967:B967">
+    <cfRule type="expression" dxfId="6" priority="257">
+      <formula>B967&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B968:B968">
+    <cfRule type="expression" dxfId="6" priority="256">
+      <formula>B968&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B980:B980">
+    <cfRule type="expression" dxfId="6" priority="255">
+      <formula>B980&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B991:B991">
+    <cfRule type="expression" dxfId="6" priority="254">
+      <formula>B991&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B999:B999">
+    <cfRule type="expression" dxfId="6" priority="253">
+      <formula>B999&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1013:B1013">
+    <cfRule type="expression" dxfId="6" priority="252">
+      <formula>B1013&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1014:B1014">
+    <cfRule type="expression" dxfId="6" priority="251">
+      <formula>B1014&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1025:B1025">
+    <cfRule type="expression" dxfId="6" priority="250">
+      <formula>B1025&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1035:B1035">
+    <cfRule type="expression" dxfId="6" priority="249">
+      <formula>B1035&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1039:B1039">
+    <cfRule type="expression" dxfId="6" priority="248">
+      <formula>B1039&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1046:B1046">
+    <cfRule type="expression" dxfId="6" priority="247">
+      <formula>B1046&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1105:B1105">
+    <cfRule type="expression" dxfId="8" priority="246">
+      <formula>B1105&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1106:B1106">
+    <cfRule type="expression" dxfId="8" priority="245">
+      <formula>B1106&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1115:B1115">
+    <cfRule type="expression" dxfId="8" priority="244">
+      <formula>B1115&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1123:B1123">
+    <cfRule type="expression" dxfId="8" priority="243">
+      <formula>B1123&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1151:B1151">
+    <cfRule type="expression" dxfId="8" priority="242">
+      <formula>B1151&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1152:B1152">
+    <cfRule type="expression" dxfId="8" priority="241">
+      <formula>B1152&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1160:B1160">
+    <cfRule type="expression" dxfId="8" priority="240">
+      <formula>B1160&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1170:B1170">
+    <cfRule type="expression" dxfId="8" priority="239">
+      <formula>B1170&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1182:B1182">
+    <cfRule type="expression" dxfId="8" priority="238">
+      <formula>B1182&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1197:B1197">
+    <cfRule type="expression" dxfId="8" priority="237">
+      <formula>B1197&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1198:B1198">
+    <cfRule type="expression" dxfId="8" priority="236">
+      <formula>B1198&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1207:B1207">
+    <cfRule type="expression" dxfId="8" priority="235">
+      <formula>B1207&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1216:B1216">
+    <cfRule type="expression" dxfId="8" priority="234">
+      <formula>B1216&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1225:B1225">
+    <cfRule type="expression" dxfId="8" priority="233">
+      <formula>B1225&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1232:B1232">
+    <cfRule type="expression" dxfId="8" priority="232">
+      <formula>B1232&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1243:B1243">
+    <cfRule type="expression" dxfId="8" priority="231">
+      <formula>B1243&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1244:B1244">
+    <cfRule type="expression" dxfId="8" priority="230">
+      <formula>B1244&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1255:B1255">
+    <cfRule type="expression" dxfId="8" priority="229">
+      <formula>B1255&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1259:B1259">
+    <cfRule type="expression" dxfId="8" priority="228">
+      <formula>B1259&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:A15">
+    <cfRule type="expression" dxfId="9" priority="227">
+      <formula>A15&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A35">
+    <cfRule type="expression" dxfId="9" priority="226">
+      <formula>A35&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52:A52">
+    <cfRule type="expression" dxfId="9" priority="225">
+      <formula>A52&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:A53">
+    <cfRule type="expression" dxfId="9" priority="224">
+      <formula>A53&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:A55">
+    <cfRule type="expression" dxfId="9" priority="223">
+      <formula>A55&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:A56">
+    <cfRule type="expression" dxfId="9" priority="222">
+      <formula>A56&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64:A64">
+    <cfRule type="expression" dxfId="9" priority="221">
+      <formula>A64&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65:A65">
+    <cfRule type="expression" dxfId="9" priority="220">
+      <formula>A65&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68:A68">
+    <cfRule type="expression" dxfId="9" priority="219">
+      <formula>A68&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A77:A77">
+    <cfRule type="expression" dxfId="9" priority="218">
+      <formula>A77&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80:A80">
+    <cfRule type="expression" dxfId="9" priority="217">
+      <formula>A80&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A89:A89">
+    <cfRule type="expression" dxfId="9" priority="216">
+      <formula>A89&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A97:A97">
+    <cfRule type="expression" dxfId="9" priority="215">
+      <formula>A97&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A100:A100">
+    <cfRule type="expression" dxfId="9" priority="214">
+      <formula>A100&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A115:A115">
+    <cfRule type="expression" dxfId="9" priority="213">
+      <formula>A115&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A117:A117">
+    <cfRule type="expression" dxfId="9" priority="212">
+      <formula>A117&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A124:A124">
+    <cfRule type="expression" dxfId="9" priority="211">
+      <formula>A124&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A125:A125">
+    <cfRule type="expression" dxfId="9" priority="210">
+      <formula>A125&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A132:A132">
+    <cfRule type="expression" dxfId="9" priority="209">
+      <formula>A132&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A148:A148">
+    <cfRule type="expression" dxfId="9" priority="208">
+      <formula>A148&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A149:A149">
+    <cfRule type="expression" dxfId="9" priority="207">
+      <formula>A149&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A150:A150">
+    <cfRule type="expression" dxfId="9" priority="206">
+      <formula>A150&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A151:A151">
+    <cfRule type="expression" dxfId="9" priority="205">
+      <formula>A151&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A152:A152">
+    <cfRule type="expression" dxfId="9" priority="204">
+      <formula>A152&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A189:A189">
+    <cfRule type="expression" dxfId="9" priority="203">
+      <formula>A189&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A193:A193">
+    <cfRule type="expression" dxfId="9" priority="202">
+      <formula>A193&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A201:A201">
+    <cfRule type="expression" dxfId="9" priority="201">
+      <formula>A201&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A207:A207">
+    <cfRule type="expression" dxfId="9" priority="200">
+      <formula>A207&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A208:A208">
+    <cfRule type="expression" dxfId="9" priority="199">
+      <formula>A208&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A209:A209">
+    <cfRule type="expression" dxfId="9" priority="198">
+      <formula>A209&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A217:A217">
+    <cfRule type="expression" dxfId="9" priority="197">
+      <formula>A217&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A236:A236">
+    <cfRule type="expression" dxfId="9" priority="196">
+      <formula>A236&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A241:A241">
+    <cfRule type="expression" dxfId="9" priority="195">
+      <formula>A241&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A248:A248">
+    <cfRule type="expression" dxfId="9" priority="194">
+      <formula>A248&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A251:A251">
+    <cfRule type="expression" dxfId="9" priority="193">
+      <formula>A251&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A257:A257">
+    <cfRule type="expression" dxfId="9" priority="192">
+      <formula>A257&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A258:A258">
+    <cfRule type="expression" dxfId="9" priority="191">
+      <formula>A258&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A268:A268">
+    <cfRule type="expression" dxfId="9" priority="190">
+      <formula>A268&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A271:A271">
+    <cfRule type="expression" dxfId="9" priority="189">
+      <formula>A271&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A282:A282">
+    <cfRule type="expression" dxfId="9" priority="188">
+      <formula>A282&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A374:A374">
+    <cfRule type="expression" dxfId="9" priority="187">
+      <formula>A374&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A403:A403">
+    <cfRule type="expression" dxfId="9" priority="186">
+      <formula>A403&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A404:A404">
+    <cfRule type="expression" dxfId="9" priority="185">
+      <formula>A404&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A406:A406">
+    <cfRule type="expression" dxfId="9" priority="184">
+      <formula>A406&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A407:A407">
+    <cfRule type="expression" dxfId="9" priority="183">
+      <formula>A407&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A558:A558">
+    <cfRule type="expression" dxfId="9" priority="182">
+      <formula>A558&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A561:A561">
+    <cfRule type="expression" dxfId="9" priority="181">
+      <formula>A561&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A570:A570">
+    <cfRule type="expression" dxfId="9" priority="180">
+      <formula>A570&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A579:A579">
+    <cfRule type="expression" dxfId="9" priority="179">
+      <formula>A579&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A581:A581">
+    <cfRule type="expression" dxfId="9" priority="178">
+      <formula>A581&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A591:A591">
+    <cfRule type="expression" dxfId="9" priority="177">
+      <formula>A591&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A592:A592">
+    <cfRule type="expression" dxfId="9" priority="176">
+      <formula>A592&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A607:A607">
+    <cfRule type="expression" dxfId="9" priority="175">
+      <formula>A607&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A610:A610">
+    <cfRule type="expression" dxfId="9" priority="174">
+      <formula>A610&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A612:A612">
+    <cfRule type="expression" dxfId="9" priority="173">
+      <formula>A612&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A621:A621">
+    <cfRule type="expression" dxfId="9" priority="172">
+      <formula>A621&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A630:A630">
+    <cfRule type="expression" dxfId="9" priority="171">
+      <formula>A630&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A637:A637">
+    <cfRule type="expression" dxfId="9" priority="170">
+      <formula>A637&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A660:A660">
+    <cfRule type="expression" dxfId="9" priority="169">
+      <formula>A660&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A668:A668">
+    <cfRule type="expression" dxfId="9" priority="168">
+      <formula>A668&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A669:A669">
+    <cfRule type="expression" dxfId="9" priority="167">
+      <formula>A669&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A670:A670">
+    <cfRule type="expression" dxfId="9" priority="166">
+      <formula>A670&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A677:A677">
+    <cfRule type="expression" dxfId="9" priority="165">
+      <formula>A677&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A697:A697">
+    <cfRule type="expression" dxfId="9" priority="164">
+      <formula>A697&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A699:A699">
+    <cfRule type="expression" dxfId="9" priority="163">
+      <formula>A699&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A700:A700">
+    <cfRule type="expression" dxfId="9" priority="162">
+      <formula>A700&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A707:A707">
+    <cfRule type="expression" dxfId="9" priority="161">
+      <formula>A707&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A708:A708">
+    <cfRule type="expression" dxfId="9" priority="160">
+      <formula>A708&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A713:A713">
+    <cfRule type="expression" dxfId="9" priority="159">
+      <formula>A713&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A716:A716">
+    <cfRule type="expression" dxfId="9" priority="158">
+      <formula>A716&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A728:A728">
+    <cfRule type="expression" dxfId="9" priority="157">
+      <formula>A728&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A742:A742">
+    <cfRule type="expression" dxfId="9" priority="156">
+      <formula>A742&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A745:A745">
+    <cfRule type="expression" dxfId="9" priority="155">
+      <formula>A745&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A792:A792">
+    <cfRule type="expression" dxfId="9" priority="154">
+      <formula>A792&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A822:A822">
+    <cfRule type="expression" dxfId="9" priority="153">
+      <formula>A822&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A833:A833">
+    <cfRule type="expression" dxfId="9" priority="152">
+      <formula>A833&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A857:A857">
+    <cfRule type="expression" dxfId="9" priority="151">
+      <formula>A857&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A859:A859">
+    <cfRule type="expression" dxfId="9" priority="150">
+      <formula>A859&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A971:A971">
+    <cfRule type="expression" dxfId="9" priority="149">
+      <formula>A971&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A973:A973">
+    <cfRule type="expression" dxfId="9" priority="148">
+      <formula>A973&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A974:A974">
+    <cfRule type="expression" dxfId="9" priority="147">
+      <formula>A974&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A987:A987">
+    <cfRule type="expression" dxfId="9" priority="146">
+      <formula>A987&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A988:A988">
+    <cfRule type="expression" dxfId="9" priority="145">
+      <formula>A988&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A989:A989">
+    <cfRule type="expression" dxfId="9" priority="144">
+      <formula>A989&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A992:A992">
+    <cfRule type="expression" dxfId="9" priority="143">
+      <formula>A992&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1000:A1000">
+    <cfRule type="expression" dxfId="9" priority="142">
+      <formula>A1000&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1019:A1019">
+    <cfRule type="expression" dxfId="9" priority="141">
+      <formula>A1019&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1020:A1020">
+    <cfRule type="expression" dxfId="9" priority="140">
+      <formula>A1020&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1024:A1024">
+    <cfRule type="expression" dxfId="9" priority="139">
+      <formula>A1024&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1031:A1031">
+    <cfRule type="expression" dxfId="9" priority="138">
+      <formula>A1031&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1125:A1125">
+    <cfRule type="expression" dxfId="9" priority="137">
+      <formula>A1125&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1134:A1134">
+    <cfRule type="expression" dxfId="9" priority="136">
+      <formula>A1134&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1135:A1135">
+    <cfRule type="expression" dxfId="9" priority="135">
+      <formula>A1135&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1143:A1143">
+    <cfRule type="expression" dxfId="9" priority="134">
+      <formula>A1143&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1144:A1144">
+    <cfRule type="expression" dxfId="9" priority="133">
+      <formula>A1144&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1145:A1145">
+    <cfRule type="expression" dxfId="9" priority="132">
+      <formula>A1145&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1166:A1166">
+    <cfRule type="expression" dxfId="9" priority="131">
+      <formula>A1166&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1167:A1167">
+    <cfRule type="expression" dxfId="9" priority="130">
+      <formula>A1167&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1183:A1183">
+    <cfRule type="expression" dxfId="9" priority="129">
+      <formula>A1183&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1203:A1203">
+    <cfRule type="expression" dxfId="9" priority="128">
+      <formula>A1203&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1211:A1211">
+    <cfRule type="expression" dxfId="9" priority="127">
+      <formula>A1211&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1221:A1221">
+    <cfRule type="expression" dxfId="9" priority="126">
+      <formula>A1221&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1230:A1230">
+    <cfRule type="expression" dxfId="9" priority="125">
+      <formula>A1230&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1235:A1235">
+    <cfRule type="expression" dxfId="9" priority="124">
+      <formula>A1235&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1236:A1236">
+    <cfRule type="expression" dxfId="9" priority="123">
+      <formula>A1236&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1255:A1255">
-    <cfRule type="expression" dxfId="8" priority="351">
+    <cfRule type="expression" dxfId="9" priority="122">
       <formula>A1255&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1259:A1259">
-    <cfRule type="expression" dxfId="8" priority="350">
-      <formula>A1259&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1">
-    <cfRule type="expression" dxfId="0" priority="349">
-      <formula>B1&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B2">
-    <cfRule type="expression" dxfId="0" priority="348">
-      <formula>B2&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:B14">
-    <cfRule type="expression" dxfId="0" priority="347">
-      <formula>B14&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B25">
-    <cfRule type="expression" dxfId="0" priority="346">
-      <formula>B25&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B35">
-    <cfRule type="expression" dxfId="0" priority="345">
-      <formula>B35&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B47">
-    <cfRule type="expression" dxfId="0" priority="344">
-      <formula>B47&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B48">
-    <cfRule type="expression" dxfId="0" priority="343">
-      <formula>B48&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59:B59">
-    <cfRule type="expression" dxfId="0" priority="342">
-      <formula>B59&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B68">
-    <cfRule type="expression" dxfId="0" priority="341">
-      <formula>B68&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79:B79">
-    <cfRule type="expression" dxfId="0" priority="340">
-      <formula>B79&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B93:B93">
-    <cfRule type="expression" dxfId="0" priority="339">
-      <formula>B93&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B94:B94">
-    <cfRule type="expression" dxfId="0" priority="338">
-      <formula>B94&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B103:B103">
-    <cfRule type="expression" dxfId="0" priority="337">
-      <formula>B103&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B113:B113">
-    <cfRule type="expression" dxfId="0" priority="336">
-      <formula>B113&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B124:B124">
-    <cfRule type="expression" dxfId="0" priority="335">
-      <formula>B124&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B139:B139">
-    <cfRule type="expression" dxfId="0" priority="334">
-      <formula>B139&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B140:B140">
-    <cfRule type="expression" dxfId="0" priority="333">
-      <formula>B140&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B148:B148">
-    <cfRule type="expression" dxfId="0" priority="332">
-      <formula>B148&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B185:B185">
-    <cfRule type="expression" dxfId="1" priority="331">
-      <formula>B185&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B186:B186">
-    <cfRule type="expression" dxfId="1" priority="330">
-      <formula>B186&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B194:B194">
-    <cfRule type="expression" dxfId="1" priority="329">
-      <formula>B194&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B208:B208">
-    <cfRule type="expression" dxfId="1" priority="328">
-      <formula>B208&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B217:B217">
-    <cfRule type="expression" dxfId="1" priority="327">
-      <formula>B217&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B231:B231">
-    <cfRule type="expression" dxfId="1" priority="326">
-      <formula>B231&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B232:B232">
-    <cfRule type="expression" dxfId="1" priority="325">
-      <formula>B232&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B240:B240">
-    <cfRule type="expression" dxfId="1" priority="324">
-      <formula>B240&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B253:B253">
-    <cfRule type="expression" dxfId="1" priority="323">
-      <formula>B253&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B277:B277">
-    <cfRule type="expression" dxfId="1" priority="322">
-      <formula>B277&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B278:B278">
-    <cfRule type="expression" dxfId="1" priority="321">
-      <formula>B278&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B283:B283">
-    <cfRule type="expression" dxfId="1" priority="320">
-      <formula>B283&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B291:B291">
-    <cfRule type="expression" dxfId="1" priority="319">
-      <formula>B291&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B295:B295">
-    <cfRule type="expression" dxfId="1" priority="318">
-      <formula>B295&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B323:B323">
-    <cfRule type="expression" dxfId="2" priority="317">
-      <formula>B323&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B324:B324">
-    <cfRule type="expression" dxfId="2" priority="316">
-      <formula>B324&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B334:B334">
-    <cfRule type="expression" dxfId="2" priority="315">
-      <formula>B334&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B345:B345">
-    <cfRule type="expression" dxfId="2" priority="314">
-      <formula>B345&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B353:B353">
-    <cfRule type="expression" dxfId="2" priority="313">
-      <formula>B353&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B369:B369">
-    <cfRule type="expression" dxfId="2" priority="312">
-      <formula>B369&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B370:B370">
-    <cfRule type="expression" dxfId="2" priority="311">
-      <formula>B370&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B380:B380">
-    <cfRule type="expression" dxfId="2" priority="310">
-      <formula>B380&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B390:B390">
-    <cfRule type="expression" dxfId="2" priority="309">
-      <formula>B390&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B415:B415">
-    <cfRule type="expression" dxfId="2" priority="308">
-      <formula>B415&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B416:B416">
-    <cfRule type="expression" dxfId="2" priority="307">
-      <formula>B416&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B424:B424">
-    <cfRule type="expression" dxfId="2" priority="306">
-      <formula>B424&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B461:B461">
-    <cfRule type="expression" dxfId="3" priority="305">
-      <formula>B461&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B462:B462">
-    <cfRule type="expression" dxfId="3" priority="304">
-      <formula>B462&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B475:B475">
-    <cfRule type="expression" dxfId="3" priority="303">
-      <formula>B475&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B482:B482">
-    <cfRule type="expression" dxfId="3" priority="302">
-      <formula>B482&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B507:B507">
-    <cfRule type="expression" dxfId="3" priority="301">
-      <formula>B507&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B508:B508">
-    <cfRule type="expression" dxfId="3" priority="300">
-      <formula>B508&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B553:B553">
-    <cfRule type="expression" dxfId="4" priority="299">
-      <formula>B553&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B554:B554">
-    <cfRule type="expression" dxfId="4" priority="298">
-      <formula>B554&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B562:B562">
-    <cfRule type="expression" dxfId="4" priority="297">
-      <formula>B562&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B567:B567">
-    <cfRule type="expression" dxfId="4" priority="296">
-      <formula>B567&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B576:B576">
-    <cfRule type="expression" dxfId="4" priority="295">
-      <formula>B576&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B584:B584">
-    <cfRule type="expression" dxfId="4" priority="294">
-      <formula>B584&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B599:B599">
-    <cfRule type="expression" dxfId="4" priority="293">
-      <formula>B599&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B600:B600">
-    <cfRule type="expression" dxfId="4" priority="292">
-      <formula>B600&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B609:B609">
-    <cfRule type="expression" dxfId="4" priority="291">
-      <formula>B609&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B617:B617">
-    <cfRule type="expression" dxfId="4" priority="290">
-      <formula>B617&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B630:B630">
-    <cfRule type="expression" dxfId="4" priority="289">
-      <formula>B630&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B645:B645">
-    <cfRule type="expression" dxfId="4" priority="288">
-      <formula>B645&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B646:B646">
-    <cfRule type="expression" dxfId="4" priority="287">
-      <formula>B646&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B654:B654">
-    <cfRule type="expression" dxfId="4" priority="286">
-      <formula>B654&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B662:B662">
-    <cfRule type="expression" dxfId="4" priority="285">
-      <formula>B662&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B672:B672">
-    <cfRule type="expression" dxfId="4" priority="284">
-      <formula>B672&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B691:B691">
-    <cfRule type="expression" dxfId="4" priority="283">
-      <formula>B691&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B692:B692">
-    <cfRule type="expression" dxfId="4" priority="282">
-      <formula>B692&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B697:B697">
-    <cfRule type="expression" dxfId="4" priority="281">
-      <formula>B697&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B707:B707">
-    <cfRule type="expression" dxfId="4" priority="280">
-      <formula>B707&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B715:B715">
-    <cfRule type="expression" dxfId="4" priority="279">
-      <formula>B715&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B723:B723">
-    <cfRule type="expression" dxfId="4" priority="278">
-      <formula>B723&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B727:B727">
-    <cfRule type="expression" dxfId="4" priority="277">
-      <formula>B727&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B737:B737">
-    <cfRule type="expression" dxfId="4" priority="276">
-      <formula>B737&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B738:B738">
-    <cfRule type="expression" dxfId="4" priority="275">
-      <formula>B738&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B783:B783">
-    <cfRule type="expression" dxfId="5" priority="274">
-      <formula>B783&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B784:B784">
-    <cfRule type="expression" dxfId="5" priority="273">
-      <formula>B784&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B792:B792">
-    <cfRule type="expression" dxfId="5" priority="272">
-      <formula>B792&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B801:B801">
-    <cfRule type="expression" dxfId="5" priority="271">
-      <formula>B801&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B810:B810">
-    <cfRule type="expression" dxfId="5" priority="270">
-      <formula>B810&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B829:B829">
-    <cfRule type="expression" dxfId="5" priority="269">
-      <formula>B829&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B830:B830">
-    <cfRule type="expression" dxfId="5" priority="268">
-      <formula>B830&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B841:B841">
-    <cfRule type="expression" dxfId="5" priority="267">
-      <formula>B841&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B849:B849">
-    <cfRule type="expression" dxfId="5" priority="266">
-      <formula>B849&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B858:B858">
-    <cfRule type="expression" dxfId="5" priority="265">
-      <formula>B858&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B875:B875">
-    <cfRule type="expression" dxfId="5" priority="264">
-      <formula>B875&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B876:B876">
-    <cfRule type="expression" dxfId="5" priority="263">
-      <formula>B876&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B884:B884">
-    <cfRule type="expression" dxfId="5" priority="262">
-      <formula>B884&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B893:B893">
-    <cfRule type="expression" dxfId="5" priority="261">
-      <formula>B893&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B904:B904">
-    <cfRule type="expression" dxfId="5" priority="260">
-      <formula>B904&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B921:B921">
-    <cfRule type="expression" dxfId="5" priority="259">
-      <formula>B921&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B922:B922">
-    <cfRule type="expression" dxfId="5" priority="258">
-      <formula>B922&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B932:B932">
-    <cfRule type="expression" dxfId="5" priority="257">
-      <formula>B932&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B967:B967">
-    <cfRule type="expression" dxfId="6" priority="256">
-      <formula>B967&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B968:B968">
-    <cfRule type="expression" dxfId="6" priority="255">
-      <formula>B968&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B980:B980">
-    <cfRule type="expression" dxfId="6" priority="254">
-      <formula>B980&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B991:B991">
-    <cfRule type="expression" dxfId="6" priority="253">
-      <formula>B991&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B999:B999">
-    <cfRule type="expression" dxfId="6" priority="252">
-      <formula>B999&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1013:B1013">
-    <cfRule type="expression" dxfId="6" priority="251">
-      <formula>B1013&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1014:B1014">
-    <cfRule type="expression" dxfId="6" priority="250">
-      <formula>B1014&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1025:B1025">
-    <cfRule type="expression" dxfId="6" priority="249">
-      <formula>B1025&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1035:B1035">
-    <cfRule type="expression" dxfId="6" priority="248">
-      <formula>B1035&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1039:B1039">
-    <cfRule type="expression" dxfId="6" priority="247">
-      <formula>B1039&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1046:B1046">
-    <cfRule type="expression" dxfId="6" priority="246">
-      <formula>B1046&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1105:B1105">
-    <cfRule type="expression" dxfId="8" priority="245">
-      <formula>B1105&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1106:B1106">
-    <cfRule type="expression" dxfId="8" priority="244">
-      <formula>B1106&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1115:B1115">
-    <cfRule type="expression" dxfId="8" priority="243">
-      <formula>B1115&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1123:B1123">
-    <cfRule type="expression" dxfId="8" priority="242">
-      <formula>B1123&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1146:B1146">
-    <cfRule type="expression" dxfId="8" priority="241">
-      <formula>B1146&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1151:B1151">
-    <cfRule type="expression" dxfId="8" priority="240">
-      <formula>B1151&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1152:B1152">
-    <cfRule type="expression" dxfId="8" priority="239">
-      <formula>B1152&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1160:B1160">
-    <cfRule type="expression" dxfId="8" priority="238">
-      <formula>B1160&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1167:B1167">
-    <cfRule type="expression" dxfId="8" priority="237">
-      <formula>B1167&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1175:B1175">
-    <cfRule type="expression" dxfId="8" priority="236">
-      <formula>B1175&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1184:B1184">
-    <cfRule type="expression" dxfId="8" priority="235">
-      <formula>B1184&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1197:B1197">
-    <cfRule type="expression" dxfId="8" priority="234">
-      <formula>B1197&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1198:B1198">
-    <cfRule type="expression" dxfId="8" priority="233">
-      <formula>B1198&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1207:B1207">
-    <cfRule type="expression" dxfId="8" priority="232">
-      <formula>B1207&lt;&gt;0</formula>
+  <conditionalFormatting sqref="A1256:A1256">
+    <cfRule type="expression" dxfId="9" priority="121">
+      <formula>A1256&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1257:A1257">
+    <cfRule type="expression" dxfId="9" priority="120">
+      <formula>A1257&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1258:A1258">
+    <cfRule type="expression" dxfId="9" priority="119">
+      <formula>A1258&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1267:A1267">
+    <cfRule type="expression" dxfId="9" priority="118">
+      <formula>A1267&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1268:A1268">
+    <cfRule type="expression" dxfId="9" priority="117">
+      <formula>A1268&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1269:A1269">
+    <cfRule type="expression" dxfId="9" priority="116">
+      <formula>A1269&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1270:A1270">
+    <cfRule type="expression" dxfId="9" priority="115">
+      <formula>A1270&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B5">
+    <cfRule type="expression" dxfId="9" priority="114">
+      <formula>B5&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B7">
+    <cfRule type="expression" dxfId="9" priority="113">
+      <formula>B7&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:B17">
+    <cfRule type="expression" dxfId="9" priority="112">
+      <formula>B17&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:B20">
+    <cfRule type="expression" dxfId="9" priority="111">
+      <formula>B20&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:B21">
+    <cfRule type="expression" dxfId="9" priority="110">
+      <formula>B21&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:B29">
+    <cfRule type="expression" dxfId="9" priority="109">
+      <formula>B29&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B30">
+    <cfRule type="expression" dxfId="9" priority="108">
+      <formula>B30&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B31">
+    <cfRule type="expression" dxfId="9" priority="107">
+      <formula>B31&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:B38">
+    <cfRule type="expression" dxfId="9" priority="106">
+      <formula>B38&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B39">
+    <cfRule type="expression" dxfId="9" priority="105">
+      <formula>B39&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B42">
+    <cfRule type="expression" dxfId="9" priority="104">
+      <formula>B42&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51:B51">
+    <cfRule type="expression" dxfId="9" priority="103">
+      <formula>B51&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:B52">
+    <cfRule type="expression" dxfId="9" priority="102">
+      <formula>B52&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:B55">
+    <cfRule type="expression" dxfId="9" priority="101">
+      <formula>B55&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56:B56">
+    <cfRule type="expression" dxfId="9" priority="100">
+      <formula>B56&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B63">
+    <cfRule type="expression" dxfId="9" priority="99">
+      <formula>B63&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72:B72">
+    <cfRule type="expression" dxfId="9" priority="98">
+      <formula>B72&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84:B84">
+    <cfRule type="expression" dxfId="9" priority="97">
+      <formula>B84&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B99:B99">
+    <cfRule type="expression" dxfId="9" priority="96">
+      <formula>B99&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B117:B117">
+    <cfRule type="expression" dxfId="9" priority="95">
+      <formula>B117&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B127:B127">
+    <cfRule type="expression" dxfId="9" priority="94">
+      <formula>B127&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B130:B130">
+    <cfRule type="expression" dxfId="9" priority="93">
+      <formula>B130&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142:B142">
+    <cfRule type="expression" dxfId="9" priority="92">
+      <formula>B142&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B144:B144">
+    <cfRule type="expression" dxfId="9" priority="91">
+      <formula>B144&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B153:B153">
+    <cfRule type="expression" dxfId="9" priority="90">
+      <formula>B153&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B189:B189">
+    <cfRule type="expression" dxfId="9" priority="89">
+      <formula>B189&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B190:B190">
+    <cfRule type="expression" dxfId="9" priority="88">
+      <formula>B190&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B191:B191">
+    <cfRule type="expression" dxfId="9" priority="87">
+      <formula>B191&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B192:B192">
+    <cfRule type="expression" dxfId="9" priority="86">
+      <formula>B192&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B198:B198">
+    <cfRule type="expression" dxfId="9" priority="85">
+      <formula>B198&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B199:B199">
+    <cfRule type="expression" dxfId="9" priority="84">
+      <formula>B199&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B206:B206">
+    <cfRule type="expression" dxfId="9" priority="83">
+      <formula>B206&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222:B222">
+    <cfRule type="expression" dxfId="9" priority="82">
+      <formula>B222&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236:B236">
+    <cfRule type="expression" dxfId="9" priority="81">
+      <formula>B236&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B247:B247">
+    <cfRule type="expression" dxfId="9" priority="80">
+      <formula>B247&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B286:B286">
+    <cfRule type="expression" dxfId="9" priority="79">
+      <formula>B286&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B287:B287">
+    <cfRule type="expression" dxfId="9" priority="78">
+      <formula>B287&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B327:B327">
+    <cfRule type="expression" dxfId="9" priority="77">
+      <formula>B327&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B330:B330">
+    <cfRule type="expression" dxfId="9" priority="76">
+      <formula>B330&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B340:B340">
+    <cfRule type="expression" dxfId="9" priority="75">
+      <formula>B340&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B341:B341">
+    <cfRule type="expression" dxfId="9" priority="74">
+      <formula>B341&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B342:B342">
+    <cfRule type="expression" dxfId="9" priority="73">
+      <formula>B342&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B358:B358">
+    <cfRule type="expression" dxfId="9" priority="72">
+      <formula>B358&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B362:B362">
+    <cfRule type="expression" dxfId="9" priority="71">
+      <formula>B362&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B377:B377">
+    <cfRule type="expression" dxfId="9" priority="70">
+      <formula>B377&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B378:B378">
+    <cfRule type="expression" dxfId="9" priority="69">
+      <formula>B378&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B386:B386">
+    <cfRule type="expression" dxfId="9" priority="68">
+      <formula>B386&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B387:B387">
+    <cfRule type="expression" dxfId="9" priority="67">
+      <formula>B387&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B420:B420">
+    <cfRule type="expression" dxfId="9" priority="66">
+      <formula>B420&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B421:B421">
+    <cfRule type="expression" dxfId="9" priority="65">
+      <formula>B421&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B429:B429">
+    <cfRule type="expression" dxfId="9" priority="64">
+      <formula>B429&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B557:B557">
+    <cfRule type="expression" dxfId="9" priority="63">
+      <formula>B557&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B560:B560">
+    <cfRule type="expression" dxfId="9" priority="62">
+      <formula>B560&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B571:B571">
+    <cfRule type="expression" dxfId="9" priority="61">
+      <formula>B571&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B580:B580">
+    <cfRule type="expression" dxfId="9" priority="60">
+      <formula>B580&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B581:B581">
+    <cfRule type="expression" dxfId="9" priority="59">
+      <formula>B581&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B587:B587">
+    <cfRule type="expression" dxfId="9" priority="58">
+      <formula>B587&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B589:B589">
+    <cfRule type="expression" dxfId="9" priority="57">
+      <formula>B589&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B603:B603">
+    <cfRule type="expression" dxfId="9" priority="56">
+      <formula>B603&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B613:B613">
+    <cfRule type="expression" dxfId="9" priority="55">
+      <formula>B613&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B614:B614">
+    <cfRule type="expression" dxfId="9" priority="54">
+      <formula>B614&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B615:B615">
+    <cfRule type="expression" dxfId="9" priority="53">
+      <formula>B615&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B626:B626">
+    <cfRule type="expression" dxfId="9" priority="52">
+      <formula>B626&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B652:B652">
+    <cfRule type="expression" dxfId="9" priority="51">
+      <formula>B652&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B657:B657">
+    <cfRule type="expression" dxfId="9" priority="50">
+      <formula>B657&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B660:B660">
+    <cfRule type="expression" dxfId="9" priority="49">
+      <formula>B660&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B668:B668">
+    <cfRule type="expression" dxfId="9" priority="48">
+      <formula>B668&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B678:B678">
+    <cfRule type="expression" dxfId="9" priority="47">
+      <formula>B678&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B680:B680">
+    <cfRule type="expression" dxfId="9" priority="46">
+      <formula>B680&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B701:B701">
+    <cfRule type="expression" dxfId="9" priority="45">
+      <formula>B701&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B702:B702">
+    <cfRule type="expression" dxfId="9" priority="44">
+      <formula>B702&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B703:B703">
+    <cfRule type="expression" dxfId="9" priority="43">
+      <formula>B703&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B712:B712">
+    <cfRule type="expression" dxfId="9" priority="42">
+      <formula>B712&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B732:B732">
+    <cfRule type="expression" dxfId="9" priority="41">
+      <formula>B732&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B741:B741">
+    <cfRule type="expression" dxfId="9" priority="40">
+      <formula>B741&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B804:B804">
+    <cfRule type="expression" dxfId="9" priority="39">
+      <formula>B804&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B844:B844">
+    <cfRule type="expression" dxfId="9" priority="38">
+      <formula>B844&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B846:B846">
+    <cfRule type="expression" dxfId="9" priority="37">
+      <formula>B846&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B886:B886">
+    <cfRule type="expression" dxfId="9" priority="36">
+      <formula>B886&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B907:B907">
+    <cfRule type="expression" dxfId="9" priority="35">
+      <formula>B907&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B925:B925">
+    <cfRule type="expression" dxfId="9" priority="34">
+      <formula>B925&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B927:B927">
+    <cfRule type="expression" dxfId="9" priority="33">
+      <formula>B927&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B928:B928">
+    <cfRule type="expression" dxfId="9" priority="32">
+      <formula>B928&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B974:B974">
+    <cfRule type="expression" dxfId="9" priority="31">
+      <formula>B974&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B975:B975">
+    <cfRule type="expression" dxfId="9" priority="30">
+      <formula>B975&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B976:B976">
+    <cfRule type="expression" dxfId="9" priority="29">
+      <formula>B976&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B983:B983">
+    <cfRule type="expression" dxfId="9" priority="28">
+      <formula>B983&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B989:B989">
+    <cfRule type="expression" dxfId="9" priority="27">
+      <formula>B989&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B996:B996">
+    <cfRule type="expression" dxfId="9" priority="26">
+      <formula>B996&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1018:B1018">
+    <cfRule type="expression" dxfId="9" priority="25">
+      <formula>B1018&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1022:B1022">
+    <cfRule type="expression" dxfId="9" priority="24">
+      <formula>B1022&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1023:B1023">
+    <cfRule type="expression" dxfId="9" priority="23">
+      <formula>B1023&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1028:B1028">
+    <cfRule type="expression" dxfId="9" priority="22">
+      <formula>B1028&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1029:B1029">
+    <cfRule type="expression" dxfId="9" priority="21">
+      <formula>B1029&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1030:B1030">
+    <cfRule type="expression" dxfId="9" priority="20">
+      <formula>B1030&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1032:B1032">
+    <cfRule type="expression" dxfId="9" priority="19">
+      <formula>B1032&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1033:B1033">
+    <cfRule type="expression" dxfId="9" priority="18">
+      <formula>B1033&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1051:B1051">
+    <cfRule type="expression" dxfId="9" priority="17">
+      <formula>B1051&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1109:B1109">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>B1109&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1118:B1118">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>B1118&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1120:B1120">
+    <cfRule type="expression" dxfId="9" priority="14">
+      <formula>B1120&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1121:B1121">
+    <cfRule type="expression" dxfId="9" priority="13">
+      <formula>B1121&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1129:B1129">
+    <cfRule type="expression" dxfId="9" priority="12">
+      <formula>B1129&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1163:B1163">
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>B1163&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1173:B1173">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>B1173&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1185:B1185">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>B1185&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1187:B1187">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>B1187&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1219:B1219">
-    <cfRule type="expression" dxfId="8" priority="231">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>B1219&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1231:B1231">
-    <cfRule type="expression" dxfId="8" priority="230">
-      <formula>B1231&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1243:B1243">
-    <cfRule type="expression" dxfId="8" priority="229">
-      <formula>B1243&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1244:B1244">
-    <cfRule type="expression" dxfId="8" priority="228">
-      <formula>B1244&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1252:B1252">
-    <cfRule type="expression" dxfId="8" priority="227">
-      <formula>B1252&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1256:B1256">
-    <cfRule type="expression" dxfId="8" priority="226">
-      <formula>B1256&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A15">
-    <cfRule type="expression" dxfId="9" priority="225">
-      <formula>A15&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A35">
-    <cfRule type="expression" dxfId="9" priority="224">
-      <formula>A35&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52:A52">
-    <cfRule type="expression" dxfId="9" priority="223">
-      <formula>A52&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53:A53">
-    <cfRule type="expression" dxfId="9" priority="222">
-      <formula>A53&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55:A55">
-    <cfRule type="expression" dxfId="9" priority="221">
-      <formula>A55&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56:A56">
-    <cfRule type="expression" dxfId="9" priority="220">
-      <formula>A56&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A64:A64">
-    <cfRule type="expression" dxfId="9" priority="219">
-      <formula>A64&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65:A65">
-    <cfRule type="expression" dxfId="9" priority="218">
-      <formula>A65&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A68:A68">
-    <cfRule type="expression" dxfId="9" priority="217">
-      <formula>A68&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A77:A77">
-    <cfRule type="expression" dxfId="9" priority="216">
-      <formula>A77&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A80:A80">
-    <cfRule type="expression" dxfId="9" priority="215">
-      <formula>A80&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A89:A89">
-    <cfRule type="expression" dxfId="9" priority="214">
-      <formula>A89&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A97:A97">
-    <cfRule type="expression" dxfId="9" priority="213">
-      <formula>A97&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A100:A100">
-    <cfRule type="expression" dxfId="9" priority="212">
-      <formula>A100&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A115:A115">
-    <cfRule type="expression" dxfId="9" priority="211">
-      <formula>A115&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A117:A117">
-    <cfRule type="expression" dxfId="9" priority="210">
-      <formula>A117&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A124:A124">
-    <cfRule type="expression" dxfId="9" priority="209">
-      <formula>A124&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A125:A125">
-    <cfRule type="expression" dxfId="9" priority="208">
-      <formula>A125&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A132:A132">
-    <cfRule type="expression" dxfId="9" priority="207">
-      <formula>A132&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A148:A148">
-    <cfRule type="expression" dxfId="9" priority="206">
-      <formula>A148&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A149:A149">
-    <cfRule type="expression" dxfId="9" priority="205">
-      <formula>A149&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A150:A150">
-    <cfRule type="expression" dxfId="9" priority="204">
-      <formula>A150&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A151:A151">
-    <cfRule type="expression" dxfId="9" priority="203">
-      <formula>A151&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A152:A152">
-    <cfRule type="expression" dxfId="9" priority="202">
-      <formula>A152&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A189:A189">
-    <cfRule type="expression" dxfId="9" priority="201">
-      <formula>A189&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A193:A193">
-    <cfRule type="expression" dxfId="9" priority="200">
-      <formula>A193&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A201:A201">
-    <cfRule type="expression" dxfId="9" priority="199">
-      <formula>A201&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A207:A207">
-    <cfRule type="expression" dxfId="9" priority="198">
-      <formula>A207&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A208:A208">
-    <cfRule type="expression" dxfId="9" priority="197">
-      <formula>A208&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A209:A209">
-    <cfRule type="expression" dxfId="9" priority="196">
-      <formula>A209&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A217:A217">
-    <cfRule type="expression" dxfId="9" priority="195">
-      <formula>A217&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A236:A236">
-    <cfRule type="expression" dxfId="9" priority="194">
-      <formula>A236&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A241:A241">
-    <cfRule type="expression" dxfId="9" priority="193">
-      <formula>A241&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A248:A248">
-    <cfRule type="expression" dxfId="9" priority="192">
-      <formula>A248&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A251:A251">
-    <cfRule type="expression" dxfId="9" priority="191">
-      <formula>A251&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A257:A257">
-    <cfRule type="expression" dxfId="9" priority="190">
-      <formula>A257&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A258:A258">
-    <cfRule type="expression" dxfId="9" priority="189">
-      <formula>A258&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A268:A268">
-    <cfRule type="expression" dxfId="9" priority="188">
-      <formula>A268&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A271:A271">
-    <cfRule type="expression" dxfId="9" priority="187">
-      <formula>A271&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A282:A282">
-    <cfRule type="expression" dxfId="9" priority="186">
-      <formula>A282&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A374:A374">
-    <cfRule type="expression" dxfId="9" priority="185">
-      <formula>A374&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A403:A403">
-    <cfRule type="expression" dxfId="9" priority="184">
-      <formula>A403&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A404:A404">
-    <cfRule type="expression" dxfId="9" priority="183">
-      <formula>A404&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A406:A406">
-    <cfRule type="expression" dxfId="9" priority="182">
-      <formula>A406&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A407:A407">
-    <cfRule type="expression" dxfId="9" priority="181">
-      <formula>A407&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A558:A558">
-    <cfRule type="expression" dxfId="9" priority="180">
-      <formula>A558&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A561:A561">
-    <cfRule type="expression" dxfId="9" priority="179">
-      <formula>A561&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A570:A570">
-    <cfRule type="expression" dxfId="9" priority="178">
-      <formula>A570&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A579:A579">
-    <cfRule type="expression" dxfId="9" priority="177">
-      <formula>A579&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A581:A581">
-    <cfRule type="expression" dxfId="9" priority="176">
-      <formula>A581&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A591:A591">
-    <cfRule type="expression" dxfId="9" priority="175">
-      <formula>A591&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A592:A592">
-    <cfRule type="expression" dxfId="9" priority="174">
-      <formula>A592&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A607:A607">
-    <cfRule type="expression" dxfId="9" priority="173">
-      <formula>A607&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A610:A610">
-    <cfRule type="expression" dxfId="9" priority="172">
-      <formula>A610&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A612:A612">
-    <cfRule type="expression" dxfId="9" priority="171">
-      <formula>A612&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A621:A621">
-    <cfRule type="expression" dxfId="9" priority="170">
-      <formula>A621&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A630:A630">
-    <cfRule type="expression" dxfId="9" priority="169">
-      <formula>A630&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A637:A637">
-    <cfRule type="expression" dxfId="9" priority="168">
-      <formula>A637&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A660:A660">
-    <cfRule type="expression" dxfId="9" priority="167">
-      <formula>A660&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A668:A668">
-    <cfRule type="expression" dxfId="9" priority="166">
-      <formula>A668&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A669:A669">
-    <cfRule type="expression" dxfId="9" priority="165">
-      <formula>A669&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A670:A670">
-    <cfRule type="expression" dxfId="9" priority="164">
-      <formula>A670&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A677:A677">
-    <cfRule type="expression" dxfId="9" priority="163">
-      <formula>A677&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A697:A697">
-    <cfRule type="expression" dxfId="9" priority="162">
-      <formula>A697&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A699:A699">
-    <cfRule type="expression" dxfId="9" priority="161">
-      <formula>A699&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A700:A700">
-    <cfRule type="expression" dxfId="9" priority="160">
-      <formula>A700&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A707:A707">
-    <cfRule type="expression" dxfId="9" priority="159">
-      <formula>A707&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A708:A708">
-    <cfRule type="expression" dxfId="9" priority="158">
-      <formula>A708&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A713:A713">
-    <cfRule type="expression" dxfId="9" priority="157">
-      <formula>A713&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A716:A716">
-    <cfRule type="expression" dxfId="9" priority="156">
-      <formula>A716&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A728:A728">
-    <cfRule type="expression" dxfId="9" priority="155">
-      <formula>A728&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A742:A742">
-    <cfRule type="expression" dxfId="9" priority="154">
-      <formula>A742&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A745:A745">
-    <cfRule type="expression" dxfId="9" priority="153">
-      <formula>A745&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A792:A792">
-    <cfRule type="expression" dxfId="9" priority="152">
-      <formula>A792&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A822:A822">
-    <cfRule type="expression" dxfId="9" priority="151">
-      <formula>A822&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A833:A833">
-    <cfRule type="expression" dxfId="9" priority="150">
-      <formula>A833&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A857:A857">
-    <cfRule type="expression" dxfId="9" priority="149">
-      <formula>A857&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A859:A859">
-    <cfRule type="expression" dxfId="9" priority="148">
-      <formula>A859&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A971:A971">
-    <cfRule type="expression" dxfId="9" priority="147">
-      <formula>A971&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A973:A973">
-    <cfRule type="expression" dxfId="9" priority="146">
-      <formula>A973&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A974:A974">
-    <cfRule type="expression" dxfId="9" priority="145">
-      <formula>A974&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A987:A987">
-    <cfRule type="expression" dxfId="9" priority="144">
-      <formula>A987&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A988:A988">
-    <cfRule type="expression" dxfId="9" priority="143">
-      <formula>A988&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A989:A989">
-    <cfRule type="expression" dxfId="9" priority="142">
-      <formula>A989&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A992:A992">
-    <cfRule type="expression" dxfId="9" priority="141">
-      <formula>A992&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1000:A1000">
-    <cfRule type="expression" dxfId="9" priority="140">
-      <formula>A1000&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1019:A1019">
-    <cfRule type="expression" dxfId="9" priority="139">
-      <formula>A1019&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1020:A1020">
-    <cfRule type="expression" dxfId="9" priority="138">
-      <formula>A1020&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1024:A1024">
-    <cfRule type="expression" dxfId="9" priority="137">
-      <formula>A1024&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1031:A1031">
-    <cfRule type="expression" dxfId="9" priority="136">
-      <formula>A1031&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1125:A1125">
-    <cfRule type="expression" dxfId="9" priority="135">
-      <formula>A1125&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1134:A1134">
-    <cfRule type="expression" dxfId="9" priority="134">
-      <formula>A1134&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1135:A1135">
-    <cfRule type="expression" dxfId="9" priority="133">
-      <formula>A1135&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1163:A1163">
-    <cfRule type="expression" dxfId="9" priority="132">
-      <formula>A1163&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1173:A1173">
-    <cfRule type="expression" dxfId="9" priority="131">
-      <formula>A1173&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1185:A1185">
-    <cfRule type="expression" dxfId="9" priority="130">
-      <formula>A1185&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1187:A1187">
-    <cfRule type="expression" dxfId="9" priority="129">
-      <formula>A1187&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1219:A1219">
-    <cfRule type="expression" dxfId="9" priority="128">
-      <formula>A1219&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1222:A1222">
-    <cfRule type="expression" dxfId="9" priority="127">
-      <formula>A1222&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1228:A1228">
-    <cfRule type="expression" dxfId="9" priority="126">
-      <formula>A1228&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1264:A1264">
-    <cfRule type="expression" dxfId="9" priority="125">
-      <formula>A1264&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1265:A1265">
-    <cfRule type="expression" dxfId="9" priority="124">
-      <formula>A1265&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B5">
-    <cfRule type="expression" dxfId="9" priority="123">
-      <formula>B5&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B7">
-    <cfRule type="expression" dxfId="9" priority="122">
-      <formula>B7&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:B17">
-    <cfRule type="expression" dxfId="9" priority="121">
-      <formula>B17&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:B20">
-    <cfRule type="expression" dxfId="9" priority="120">
-      <formula>B20&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B21">
-    <cfRule type="expression" dxfId="9" priority="119">
-      <formula>B21&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B29">
-    <cfRule type="expression" dxfId="9" priority="118">
-      <formula>B29&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B30">
-    <cfRule type="expression" dxfId="9" priority="117">
-      <formula>B30&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B31">
-    <cfRule type="expression" dxfId="9" priority="116">
-      <formula>B31&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:B38">
-    <cfRule type="expression" dxfId="9" priority="115">
-      <formula>B38&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B39">
-    <cfRule type="expression" dxfId="9" priority="114">
-      <formula>B39&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B42">
-    <cfRule type="expression" dxfId="9" priority="113">
-      <formula>B42&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51:B51">
-    <cfRule type="expression" dxfId="9" priority="112">
-      <formula>B51&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B52">
-    <cfRule type="expression" dxfId="9" priority="111">
-      <formula>B52&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:B55">
-    <cfRule type="expression" dxfId="9" priority="110">
-      <formula>B55&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56:B56">
-    <cfRule type="expression" dxfId="9" priority="109">
-      <formula>B56&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B63">
-    <cfRule type="expression" dxfId="9" priority="108">
-      <formula>B63&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72:B72">
-    <cfRule type="expression" dxfId="9" priority="107">
-      <formula>B72&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B84:B84">
-    <cfRule type="expression" dxfId="9" priority="106">
-      <formula>B84&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B99:B99">
-    <cfRule type="expression" dxfId="9" priority="105">
-      <formula>B99&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B117:B117">
-    <cfRule type="expression" dxfId="9" priority="104">
-      <formula>B117&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B127:B127">
-    <cfRule type="expression" dxfId="9" priority="103">
-      <formula>B127&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B130:B130">
-    <cfRule type="expression" dxfId="9" priority="102">
-      <formula>B130&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142:B142">
-    <cfRule type="expression" dxfId="9" priority="101">
-      <formula>B142&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B144:B144">
-    <cfRule type="expression" dxfId="9" priority="100">
-      <formula>B144&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B153:B153">
-    <cfRule type="expression" dxfId="9" priority="99">
-      <formula>B153&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B189:B189">
-    <cfRule type="expression" dxfId="9" priority="98">
-      <formula>B189&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B190:B190">
-    <cfRule type="expression" dxfId="9" priority="97">
-      <formula>B190&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B191:B191">
-    <cfRule type="expression" dxfId="9" priority="96">
-      <formula>B191&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B192:B192">
-    <cfRule type="expression" dxfId="9" priority="95">
-      <formula>B192&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B198:B198">
-    <cfRule type="expression" dxfId="9" priority="94">
-      <formula>B198&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B199:B199">
-    <cfRule type="expression" dxfId="9" priority="93">
-      <formula>B199&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B206:B206">
-    <cfRule type="expression" dxfId="9" priority="92">
-      <formula>B206&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222:B222">
-    <cfRule type="expression" dxfId="9" priority="91">
-      <formula>B222&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B236:B236">
-    <cfRule type="expression" dxfId="9" priority="90">
-      <formula>B236&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B247:B247">
-    <cfRule type="expression" dxfId="9" priority="89">
-      <formula>B247&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B286:B286">
-    <cfRule type="expression" dxfId="9" priority="88">
-      <formula>B286&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B287:B287">
-    <cfRule type="expression" dxfId="9" priority="87">
-      <formula>B287&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B327:B327">
-    <cfRule type="expression" dxfId="9" priority="86">
-      <formula>B327&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B330:B330">
-    <cfRule type="expression" dxfId="9" priority="85">
-      <formula>B330&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B340:B340">
-    <cfRule type="expression" dxfId="9" priority="84">
-      <formula>B340&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B341:B341">
-    <cfRule type="expression" dxfId="9" priority="83">
-      <formula>B341&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B342:B342">
-    <cfRule type="expression" dxfId="9" priority="82">
-      <formula>B342&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B358:B358">
-    <cfRule type="expression" dxfId="9" priority="81">
-      <formula>B358&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B362:B362">
-    <cfRule type="expression" dxfId="9" priority="80">
-      <formula>B362&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B377:B377">
-    <cfRule type="expression" dxfId="9" priority="79">
-      <formula>B377&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B378:B378">
-    <cfRule type="expression" dxfId="9" priority="78">
-      <formula>B378&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B386:B386">
-    <cfRule type="expression" dxfId="9" priority="77">
-      <formula>B386&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B387:B387">
-    <cfRule type="expression" dxfId="9" priority="76">
-      <formula>B387&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B420:B420">
-    <cfRule type="expression" dxfId="9" priority="75">
-      <formula>B420&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B421:B421">
-    <cfRule type="expression" dxfId="9" priority="74">
-      <formula>B421&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B429:B429">
-    <cfRule type="expression" dxfId="9" priority="73">
-      <formula>B429&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B557:B557">
-    <cfRule type="expression" dxfId="9" priority="72">
-      <formula>B557&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B560:B560">
-    <cfRule type="expression" dxfId="9" priority="71">
-      <formula>B560&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B571:B571">
-    <cfRule type="expression" dxfId="9" priority="70">
-      <formula>B571&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B580:B580">
-    <cfRule type="expression" dxfId="9" priority="69">
-      <formula>B580&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B581:B581">
-    <cfRule type="expression" dxfId="9" priority="68">
-      <formula>B581&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B587:B587">
-    <cfRule type="expression" dxfId="9" priority="67">
-      <formula>B587&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B589:B589">
-    <cfRule type="expression" dxfId="9" priority="66">
-      <formula>B589&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B603:B603">
-    <cfRule type="expression" dxfId="9" priority="65">
-      <formula>B603&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B613:B613">
-    <cfRule type="expression" dxfId="9" priority="64">
-      <formula>B613&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B614:B614">
-    <cfRule type="expression" dxfId="9" priority="63">
-      <formula>B614&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B615:B615">
-    <cfRule type="expression" dxfId="9" priority="62">
-      <formula>B615&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B626:B626">
-    <cfRule type="expression" dxfId="9" priority="61">
-      <formula>B626&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B652:B652">
-    <cfRule type="expression" dxfId="9" priority="60">
-      <formula>B652&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B657:B657">
-    <cfRule type="expression" dxfId="9" priority="59">
-      <formula>B657&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B660:B660">
-    <cfRule type="expression" dxfId="9" priority="58">
-      <formula>B660&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B668:B668">
-    <cfRule type="expression" dxfId="9" priority="57">
-      <formula>B668&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B678:B678">
-    <cfRule type="expression" dxfId="9" priority="56">
-      <formula>B678&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B680:B680">
-    <cfRule type="expression" dxfId="9" priority="55">
-      <formula>B680&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B701:B701">
-    <cfRule type="expression" dxfId="9" priority="54">
-      <formula>B701&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B702:B702">
-    <cfRule type="expression" dxfId="9" priority="53">
-      <formula>B702&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B703:B703">
-    <cfRule type="expression" dxfId="9" priority="52">
-      <formula>B703&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B712:B712">
-    <cfRule type="expression" dxfId="9" priority="51">
-      <formula>B712&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B732:B732">
-    <cfRule type="expression" dxfId="9" priority="50">
-      <formula>B732&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B741:B741">
-    <cfRule type="expression" dxfId="9" priority="49">
-      <formula>B741&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B804:B804">
-    <cfRule type="expression" dxfId="9" priority="48">
-      <formula>B804&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B844:B844">
-    <cfRule type="expression" dxfId="9" priority="47">
-      <formula>B844&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B846:B846">
-    <cfRule type="expression" dxfId="9" priority="46">
-      <formula>B846&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B886:B886">
-    <cfRule type="expression" dxfId="9" priority="45">
-      <formula>B886&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B907:B907">
-    <cfRule type="expression" dxfId="9" priority="44">
-      <formula>B907&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B925:B925">
-    <cfRule type="expression" dxfId="9" priority="43">
-      <formula>B925&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B927:B927">
-    <cfRule type="expression" dxfId="9" priority="42">
-      <formula>B927&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B928:B928">
-    <cfRule type="expression" dxfId="9" priority="41">
-      <formula>B928&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B974:B974">
-    <cfRule type="expression" dxfId="9" priority="40">
-      <formula>B974&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B975:B975">
-    <cfRule type="expression" dxfId="9" priority="39">
-      <formula>B975&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B976:B976">
-    <cfRule type="expression" dxfId="9" priority="38">
-      <formula>B976&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B983:B983">
-    <cfRule type="expression" dxfId="9" priority="37">
-      <formula>B983&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B989:B989">
-    <cfRule type="expression" dxfId="9" priority="36">
-      <formula>B989&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B996:B996">
-    <cfRule type="expression" dxfId="9" priority="35">
-      <formula>B996&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1018:B1018">
-    <cfRule type="expression" dxfId="9" priority="34">
-      <formula>B1018&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1022:B1022">
-    <cfRule type="expression" dxfId="9" priority="33">
-      <formula>B1022&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1023:B1023">
-    <cfRule type="expression" dxfId="9" priority="32">
-      <formula>B1023&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1028:B1028">
-    <cfRule type="expression" dxfId="9" priority="31">
-      <formula>B1028&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1029:B1029">
-    <cfRule type="expression" dxfId="9" priority="30">
-      <formula>B1029&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1030:B1030">
-    <cfRule type="expression" dxfId="9" priority="29">
-      <formula>B1030&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1032:B1032">
-    <cfRule type="expression" dxfId="9" priority="28">
-      <formula>B1032&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1033:B1033">
-    <cfRule type="expression" dxfId="9" priority="27">
-      <formula>B1033&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1051:B1051">
-    <cfRule type="expression" dxfId="9" priority="26">
-      <formula>B1051&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1109:B1109">
-    <cfRule type="expression" dxfId="9" priority="25">
-      <formula>B1109&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1118:B1118">
-    <cfRule type="expression" dxfId="9" priority="24">
-      <formula>B1118&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1120:B1120">
-    <cfRule type="expression" dxfId="9" priority="23">
-      <formula>B1120&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1121:B1121">
-    <cfRule type="expression" dxfId="9" priority="22">
-      <formula>B1121&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1129:B1129">
-    <cfRule type="expression" dxfId="9" priority="21">
-      <formula>B1129&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1150:B1150">
-    <cfRule type="expression" dxfId="9" priority="20">
-      <formula>B1150&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1155:B1155">
-    <cfRule type="expression" dxfId="9" priority="19">
-      <formula>B1155&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1156:B1156">
-    <cfRule type="expression" dxfId="9" priority="18">
-      <formula>B1156&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1172:B1172">
-    <cfRule type="expression" dxfId="9" priority="17">
-      <formula>B1172&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1189:B1189">
-    <cfRule type="expression" dxfId="9" priority="16">
-      <formula>B1189&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1203:B1203">
-    <cfRule type="expression" dxfId="9" priority="15">
-      <formula>B1203&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1213:B1213">
-    <cfRule type="expression" dxfId="9" priority="14">
-      <formula>B1213&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1222:B1222">
-    <cfRule type="expression" dxfId="9" priority="13">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>B1222&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1227:B1227">
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>B1227&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1228:B1228">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>B1228&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1234:B1234">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>B1234&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1237:B1237">
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>B1237&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1246:B1246">
-    <cfRule type="expression" dxfId="9" priority="8">
-      <formula>B1246&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1247:B1247">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>B1247&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1248:B1248">
-    <cfRule type="expression" dxfId="9" priority="6">
-      <formula>B1248&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1249:B1249">
-    <cfRule type="expression" dxfId="9" priority="5">
-      <formula>B1249&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1258:B1258">
+  <conditionalFormatting sqref="B1235:B1235">
     <cfRule type="expression" dxfId="9" priority="4">
-      <formula>B1258&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1259:B1259">
+      <formula>B1235&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1238:B1238">
     <cfRule type="expression" dxfId="9" priority="3">
-      <formula>B1259&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1260:B1260">
+      <formula>B1238&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1264:B1264">
     <cfRule type="expression" dxfId="9" priority="2">
-      <formula>B1260&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1261:B1261">
+      <formula>B1264&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1265:B1265">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>B1261&lt;&gt;0</formula>
+      <formula>B1265&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
